--- a/excel/100(n)/RAW_Dataset.xlsx
+++ b/excel/100(n)/RAW_Dataset.xlsx
@@ -715,154 +715,154 @@
         <v>100.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>114800.0</v>
+        <v>110600.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>113100.0</v>
+        <v>113600.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>111300.0</v>
+        <v>112700.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>116100.0</v>
+        <v>177500.0</v>
       </c>
       <c r="G2" t="n" s="0">
-        <v>114800.0</v>
+        <v>138800.0</v>
       </c>
       <c r="H2" t="n" s="0">
-        <v>112200.0</v>
+        <v>134400.0</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>114300.0</v>
+        <v>143600.0</v>
       </c>
       <c r="J2" t="n" s="0">
-        <v>170300.0</v>
+        <v>178000.0</v>
       </c>
       <c r="K2" t="n" s="0">
-        <v>193300.0</v>
+        <v>185700.0</v>
       </c>
       <c r="L2" t="n" s="0">
-        <v>172100.0</v>
+        <v>144300.0</v>
       </c>
       <c r="M2" t="n" s="0">
-        <v>111700.0</v>
+        <v>151300.0</v>
       </c>
       <c r="N2" t="n" s="0">
-        <v>124300.0</v>
+        <v>206800.0</v>
       </c>
       <c r="O2" t="n" s="0">
-        <v>81000.0</v>
+        <v>100300.0</v>
       </c>
       <c r="P2" t="n" s="0">
+        <v>28600.0</v>
+      </c>
+      <c r="Q2" t="n" s="0">
+        <v>15800.0</v>
+      </c>
+      <c r="R2" t="n" s="0">
+        <v>31000.0</v>
+      </c>
+      <c r="S2" t="n" s="0">
+        <v>20000.0</v>
+      </c>
+      <c r="T2" t="n" s="0">
+        <v>18300.0</v>
+      </c>
+      <c r="U2" t="n" s="0">
+        <v>32900.0</v>
+      </c>
+      <c r="V2" t="n" s="0">
+        <v>32800.0</v>
+      </c>
+      <c r="W2" t="n" s="0">
+        <v>30400.0</v>
+      </c>
+      <c r="X2" t="n" s="0">
+        <v>33100.0</v>
+      </c>
+      <c r="Y2" t="n" s="0">
+        <v>29300.0</v>
+      </c>
+      <c r="Z2" t="n" s="0">
+        <v>50400.0</v>
+      </c>
+      <c r="AA2" t="n" s="0">
+        <v>87400.0</v>
+      </c>
+      <c r="AB2" t="n" s="0">
+        <v>31400.0</v>
+      </c>
+      <c r="AC2" t="n" s="0">
+        <v>28100.0</v>
+      </c>
+      <c r="AD2" t="n" s="0">
+        <v>18200.0</v>
+      </c>
+      <c r="AE2" t="n" s="0">
+        <v>16700.0</v>
+      </c>
+      <c r="AF2" t="n" s="0">
+        <v>18500.0</v>
+      </c>
+      <c r="AG2" t="n" s="0">
         <v>19600.0</v>
       </c>
-      <c r="Q2" t="n" s="0">
-        <v>30400.0</v>
-      </c>
-      <c r="R2" t="n" s="0">
-        <v>17600.0</v>
-      </c>
-      <c r="S2" t="n" s="0">
-        <v>30900.0</v>
-      </c>
-      <c r="T2" t="n" s="0">
-        <v>28600.0</v>
-      </c>
-      <c r="U2" t="n" s="0">
-        <v>34500.0</v>
-      </c>
-      <c r="V2" t="n" s="0">
-        <v>29000.0</v>
-      </c>
-      <c r="W2" t="n" s="0">
-        <v>29200.0</v>
-      </c>
-      <c r="X2" t="n" s="0">
-        <v>46700.0</v>
-      </c>
-      <c r="Y2" t="n" s="0">
-        <v>29900.0</v>
-      </c>
-      <c r="Z2" t="n" s="0">
-        <v>103100.0</v>
-      </c>
-      <c r="AA2" t="n" s="0">
-        <v>28700.0</v>
-      </c>
-      <c r="AB2" t="n" s="0">
-        <v>21300.0</v>
-      </c>
-      <c r="AC2" t="n" s="0">
-        <v>31100.0</v>
-      </c>
-      <c r="AD2" t="n" s="0">
-        <v>17600.0</v>
-      </c>
-      <c r="AE2" t="n" s="0">
-        <v>17300.0</v>
-      </c>
-      <c r="AF2" t="n" s="0">
-        <v>17100.0</v>
-      </c>
-      <c r="AG2" t="n" s="0">
-        <v>17800.0</v>
-      </c>
       <c r="AH2" t="n" s="0">
-        <v>16300.0</v>
+        <v>15500.0</v>
       </c>
       <c r="AI2" t="n" s="0">
-        <v>14700.0</v>
+        <v>16700.0</v>
       </c>
       <c r="AJ2" t="n" s="0">
-        <v>18900.0</v>
+        <v>24000.0</v>
       </c>
       <c r="AK2" t="n" s="0">
         <v>18100.0</v>
       </c>
       <c r="AL2" t="n" s="0">
-        <v>17000.0</v>
+        <v>14600.0</v>
       </c>
       <c r="AM2" t="n" s="0">
+        <v>17200.0</v>
+      </c>
+      <c r="AN2" t="n" s="0">
+        <v>20900.0</v>
+      </c>
+      <c r="AO2" t="n" s="0">
+        <v>16600.0</v>
+      </c>
+      <c r="AP2" t="n" s="0">
+        <v>17300.0</v>
+      </c>
+      <c r="AQ2" t="n" s="0">
+        <v>17800.0</v>
+      </c>
+      <c r="AR2" t="n" s="0">
+        <v>18400.0</v>
+      </c>
+      <c r="AS2" t="n" s="0">
+        <v>16900.0</v>
+      </c>
+      <c r="AT2" t="n" s="0">
+        <v>17100.0</v>
+      </c>
+      <c r="AU2" t="n" s="0">
+        <v>16800.0</v>
+      </c>
+      <c r="AV2" t="n" s="0">
+        <v>16500.0</v>
+      </c>
+      <c r="AW2" t="n" s="0">
         <v>17600.0</v>
       </c>
-      <c r="AN2" t="n" s="0">
-        <v>16200.0</v>
-      </c>
-      <c r="AO2" t="n" s="0">
-        <v>17400.0</v>
-      </c>
-      <c r="AP2" t="n" s="0">
+      <c r="AX2" t="n" s="0">
         <v>17500.0</v>
       </c>
-      <c r="AQ2" t="n" s="0">
-        <v>15300.0</v>
-      </c>
-      <c r="AR2" t="n" s="0">
-        <v>18900.0</v>
-      </c>
-      <c r="AS2" t="n" s="0">
-        <v>17700.0</v>
-      </c>
-      <c r="AT2" t="n" s="0">
-        <v>18100.0</v>
-      </c>
-      <c r="AU2" t="n" s="0">
-        <v>13700.0</v>
-      </c>
-      <c r="AV2" t="n" s="0">
-        <v>19000.0</v>
-      </c>
-      <c r="AW2" t="n" s="0">
-        <v>15600.0</v>
-      </c>
-      <c r="AX2" t="n" s="0">
+      <c r="AY2" t="n" s="0">
         <v>18200.0</v>
       </c>
-      <c r="AY2" t="n" s="0">
-        <v>18300.0</v>
-      </c>
       <c r="AZ2" t="n" s="0">
-        <v>18900.0</v>
+        <v>16700.0</v>
       </c>
     </row>
     <row r="3">
@@ -873,154 +873,154 @@
         <v>100.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>115100.0</v>
+        <v>112700.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>114800.0</v>
+        <v>112600.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>112900.0</v>
+        <v>112700.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>112800.0</v>
+        <v>172900.0</v>
       </c>
       <c r="G3" t="n" s="0">
-        <v>112700.0</v>
+        <v>140500.0</v>
       </c>
       <c r="H3" t="n" s="0">
-        <v>114000.0</v>
+        <v>137900.0</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>142300.0</v>
+        <v>149300.0</v>
       </c>
       <c r="J3" t="n" s="0">
-        <v>250800.0</v>
+        <v>180900.0</v>
       </c>
       <c r="K3" t="n" s="0">
-        <v>189000.0</v>
+        <v>173300.0</v>
       </c>
       <c r="L3" t="n" s="0">
-        <v>181400.0</v>
+        <v>121800.0</v>
       </c>
       <c r="M3" t="n" s="0">
-        <v>116300.0</v>
+        <v>142700.0</v>
       </c>
       <c r="N3" t="n" s="0">
-        <v>131100.0</v>
+        <v>196800.0</v>
       </c>
       <c r="O3" t="n" s="0">
-        <v>81300.0</v>
+        <v>73200.0</v>
       </c>
       <c r="P3" t="n" s="0">
+        <v>30200.0</v>
+      </c>
+      <c r="Q3" t="n" s="0">
+        <v>16800.0</v>
+      </c>
+      <c r="R3" t="n" s="0">
+        <v>30700.0</v>
+      </c>
+      <c r="S3" t="n" s="0">
+        <v>18200.0</v>
+      </c>
+      <c r="T3" t="n" s="0">
+        <v>21400.0</v>
+      </c>
+      <c r="U3" t="n" s="0">
+        <v>31300.0</v>
+      </c>
+      <c r="V3" t="n" s="0">
+        <v>30700.0</v>
+      </c>
+      <c r="W3" t="n" s="0">
+        <v>30600.0</v>
+      </c>
+      <c r="X3" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+      <c r="Y3" t="n" s="0">
+        <v>29900.0</v>
+      </c>
+      <c r="Z3" t="n" s="0">
+        <v>116800.0</v>
+      </c>
+      <c r="AA3" t="n" s="0">
+        <v>28900.0</v>
+      </c>
+      <c r="AB3" t="n" s="0">
+        <v>19800.0</v>
+      </c>
+      <c r="AC3" t="n" s="0">
+        <v>23100.0</v>
+      </c>
+      <c r="AD3" t="n" s="0">
+        <v>13400.0</v>
+      </c>
+      <c r="AE3" t="n" s="0">
+        <v>15700.0</v>
+      </c>
+      <c r="AF3" t="n" s="0">
+        <v>16400.0</v>
+      </c>
+      <c r="AG3" t="n" s="0">
         <v>18000.0</v>
       </c>
-      <c r="Q3" t="n" s="0">
-        <v>30300.0</v>
-      </c>
-      <c r="R3" t="n" s="0">
-        <v>19200.0</v>
-      </c>
-      <c r="S3" t="n" s="0">
-        <v>34900.0</v>
-      </c>
-      <c r="T3" t="n" s="0">
-        <v>27800.0</v>
-      </c>
-      <c r="U3" t="n" s="0">
+      <c r="AH3" t="n" s="0">
+        <v>15500.0</v>
+      </c>
+      <c r="AI3" t="n" s="0">
+        <v>16400.0</v>
+      </c>
+      <c r="AJ3" t="n" s="0">
         <v>30500.0</v>
       </c>
-      <c r="V3" t="n" s="0">
-        <v>28400.0</v>
-      </c>
-      <c r="W3" t="n" s="0">
-        <v>29900.0</v>
-      </c>
-      <c r="X3" t="n" s="0">
-        <v>41100.0</v>
-      </c>
-      <c r="Y3" t="n" s="0">
-        <v>30300.0</v>
-      </c>
-      <c r="Z3" t="n" s="0">
-        <v>60700.0</v>
-      </c>
-      <c r="AA3" t="n" s="0">
-        <v>28500.0</v>
-      </c>
-      <c r="AB3" t="n" s="0">
-        <v>17800.0</v>
-      </c>
-      <c r="AC3" t="n" s="0">
-        <v>25500.0</v>
-      </c>
-      <c r="AD3" t="n" s="0">
-        <v>18400.0</v>
-      </c>
-      <c r="AE3" t="n" s="0">
-        <v>18000.0</v>
-      </c>
-      <c r="AF3" t="n" s="0">
-        <v>18800.0</v>
-      </c>
-      <c r="AG3" t="n" s="0">
-        <v>17100.0</v>
-      </c>
-      <c r="AH3" t="n" s="0">
-        <v>17200.0</v>
-      </c>
-      <c r="AI3" t="n" s="0">
-        <v>13900.0</v>
-      </c>
-      <c r="AJ3" t="n" s="0">
-        <v>15700.0</v>
-      </c>
       <c r="AK3" t="n" s="0">
-        <v>19200.0</v>
+        <v>15900.0</v>
       </c>
       <c r="AL3" t="n" s="0">
-        <v>16800.0</v>
+        <v>17400.0</v>
       </c>
       <c r="AM3" t="n" s="0">
+        <v>20500.0</v>
+      </c>
+      <c r="AN3" t="n" s="0">
+        <v>14700.0</v>
+      </c>
+      <c r="AO3" t="n" s="0">
+        <v>18500.0</v>
+      </c>
+      <c r="AP3" t="n" s="0">
+        <v>17600.0</v>
+      </c>
+      <c r="AQ3" t="n" s="0">
+        <v>17300.0</v>
+      </c>
+      <c r="AR3" t="n" s="0">
+        <v>17600.0</v>
+      </c>
+      <c r="AS3" t="n" s="0">
+        <v>17700.0</v>
+      </c>
+      <c r="AT3" t="n" s="0">
         <v>16400.0</v>
       </c>
-      <c r="AN3" t="n" s="0">
+      <c r="AU3" t="n" s="0">
         <v>19300.0</v>
       </c>
-      <c r="AO3" t="n" s="0">
-        <v>19300.0</v>
-      </c>
-      <c r="AP3" t="n" s="0">
-        <v>16500.0</v>
-      </c>
-      <c r="AQ3" t="n" s="0">
-        <v>17500.0</v>
-      </c>
-      <c r="AR3" t="n" s="0">
+      <c r="AV3" t="n" s="0">
+        <v>19400.0</v>
+      </c>
+      <c r="AW3" t="n" s="0">
         <v>17900.0</v>
       </c>
-      <c r="AS3" t="n" s="0">
-        <v>19000.0</v>
-      </c>
-      <c r="AT3" t="n" s="0">
-        <v>16500.0</v>
-      </c>
-      <c r="AU3" t="n" s="0">
-        <v>14400.0</v>
-      </c>
-      <c r="AV3" t="n" s="0">
-        <v>15900.0</v>
-      </c>
-      <c r="AW3" t="n" s="0">
-        <v>18200.0</v>
-      </c>
       <c r="AX3" t="n" s="0">
-        <v>16700.0</v>
+        <v>18500.0</v>
       </c>
       <c r="AY3" t="n" s="0">
-        <v>18800.0</v>
+        <v>16400.0</v>
       </c>
       <c r="AZ3" t="n" s="0">
-        <v>17700.0</v>
+        <v>17300.0</v>
       </c>
     </row>
     <row r="4">
@@ -1031,154 +1031,154 @@
         <v>100.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>42000.0</v>
+        <v>115900.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>40000.0</v>
+        <v>38000.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>37100.0</v>
+        <v>39000.0</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>41600.0</v>
+        <v>61500.0</v>
       </c>
       <c r="G4" t="n" s="0">
-        <v>42700.0</v>
+        <v>47400.0</v>
       </c>
       <c r="H4" t="n" s="0">
-        <v>37100.0</v>
+        <v>40600.0</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>72000.0</v>
+        <v>60300.0</v>
       </c>
       <c r="J4" t="n" s="0">
-        <v>75800.0</v>
+        <v>58000.0</v>
       </c>
       <c r="K4" t="n" s="0">
-        <v>65100.0</v>
+        <v>62800.0</v>
       </c>
       <c r="L4" t="n" s="0">
-        <v>63500.0</v>
+        <v>39800.0</v>
       </c>
       <c r="M4" t="n" s="0">
-        <v>38700.0</v>
+        <v>47900.0</v>
       </c>
       <c r="N4" t="n" s="0">
-        <v>39400.0</v>
+        <v>69500.0</v>
       </c>
       <c r="O4" t="n" s="0">
-        <v>56400.0</v>
+        <v>94700.0</v>
       </c>
       <c r="P4" t="n" s="0">
-        <v>38900.0</v>
+        <v>60400.0</v>
       </c>
       <c r="Q4" t="n" s="0">
-        <v>56400.0</v>
+        <v>41900.0</v>
       </c>
       <c r="R4" t="n" s="0">
-        <v>45700.0</v>
+        <v>67200.0</v>
       </c>
       <c r="S4" t="n" s="0">
-        <v>59700.0</v>
+        <v>42400.0</v>
       </c>
       <c r="T4" t="n" s="0">
-        <v>56300.0</v>
+        <v>51800.0</v>
       </c>
       <c r="U4" t="n" s="0">
-        <v>60700.0</v>
+        <v>68500.0</v>
       </c>
       <c r="V4" t="n" s="0">
-        <v>60900.0</v>
+        <v>63000.0</v>
       </c>
       <c r="W4" t="n" s="0">
-        <v>62300.0</v>
+        <v>57600.0</v>
       </c>
       <c r="X4" t="n" s="0">
-        <v>62800.0</v>
+        <v>59300.0</v>
       </c>
       <c r="Y4" t="n" s="0">
-        <v>74900.0</v>
+        <v>53000.0</v>
       </c>
       <c r="Z4" t="n" s="0">
-        <v>45900.0</v>
+        <v>78000.0</v>
       </c>
       <c r="AA4" t="n" s="0">
-        <v>51700.0</v>
+        <v>50100.0</v>
       </c>
       <c r="AB4" t="n" s="0">
-        <v>13500.0</v>
+        <v>12800.0</v>
       </c>
       <c r="AC4" t="n" s="0">
-        <v>13700.0</v>
+        <v>17400.0</v>
       </c>
       <c r="AD4" t="n" s="0">
+        <v>7300.0</v>
+      </c>
+      <c r="AE4" t="n" s="0">
+        <v>9300.0</v>
+      </c>
+      <c r="AF4" t="n" s="0">
+        <v>11200.0</v>
+      </c>
+      <c r="AG4" t="n" s="0">
+        <v>14200.0</v>
+      </c>
+      <c r="AH4" t="n" s="0">
+        <v>5900.0</v>
+      </c>
+      <c r="AI4" t="n" s="0">
+        <v>10900.0</v>
+      </c>
+      <c r="AJ4" t="n" s="0">
+        <v>14300.0</v>
+      </c>
+      <c r="AK4" t="n" s="0">
+        <v>8500.0</v>
+      </c>
+      <c r="AL4" t="n" s="0">
+        <v>7000.0</v>
+      </c>
+      <c r="AM4" t="n" s="0">
+        <v>24500.0</v>
+      </c>
+      <c r="AN4" t="n" s="0">
+        <v>6300.0</v>
+      </c>
+      <c r="AO4" t="n" s="0">
+        <v>10000.0</v>
+      </c>
+      <c r="AP4" t="n" s="0">
+        <v>10100.0</v>
+      </c>
+      <c r="AQ4" t="n" s="0">
         <v>12800.0</v>
       </c>
-      <c r="AE4" t="n" s="0">
-        <v>10600.0</v>
-      </c>
-      <c r="AF4" t="n" s="0">
-        <v>10500.0</v>
-      </c>
-      <c r="AG4" t="n" s="0">
-        <v>13300.0</v>
-      </c>
-      <c r="AH4" t="n" s="0">
-        <v>9500.0</v>
-      </c>
-      <c r="AI4" t="n" s="0">
+      <c r="AR4" t="n" s="0">
+        <v>9600.0</v>
+      </c>
+      <c r="AS4" t="n" s="0">
+        <v>9700.0</v>
+      </c>
+      <c r="AT4" t="n" s="0">
+        <v>26300.0</v>
+      </c>
+      <c r="AU4" t="n" s="0">
+        <v>9200.0</v>
+      </c>
+      <c r="AV4" t="n" s="0">
+        <v>9900.0</v>
+      </c>
+      <c r="AW4" t="n" s="0">
+        <v>63000.0</v>
+      </c>
+      <c r="AX4" t="n" s="0">
+        <v>86900.0</v>
+      </c>
+      <c r="AY4" t="n" s="0">
+        <v>41200.0</v>
+      </c>
+      <c r="AZ4" t="n" s="0">
         <v>5600.0</v>
-      </c>
-      <c r="AJ4" t="n" s="0">
-        <v>14800.0</v>
-      </c>
-      <c r="AK4" t="n" s="0">
-        <v>10800.0</v>
-      </c>
-      <c r="AL4" t="n" s="0">
-        <v>10400.0</v>
-      </c>
-      <c r="AM4" t="n" s="0">
-        <v>13000.0</v>
-      </c>
-      <c r="AN4" t="n" s="0">
-        <v>9900.0</v>
-      </c>
-      <c r="AO4" t="n" s="0">
-        <v>11100.0</v>
-      </c>
-      <c r="AP4" t="n" s="0">
-        <v>10800.0</v>
-      </c>
-      <c r="AQ4" t="n" s="0">
-        <v>10400.0</v>
-      </c>
-      <c r="AR4" t="n" s="0">
-        <v>11000.0</v>
-      </c>
-      <c r="AS4" t="n" s="0">
-        <v>9200.0</v>
-      </c>
-      <c r="AT4" t="n" s="0">
-        <v>12800.0</v>
-      </c>
-      <c r="AU4" t="n" s="0">
-        <v>5500.0</v>
-      </c>
-      <c r="AV4" t="n" s="0">
-        <v>11200.0</v>
-      </c>
-      <c r="AW4" t="n" s="0">
-        <v>10400.0</v>
-      </c>
-      <c r="AX4" t="n" s="0">
-        <v>10700.0</v>
-      </c>
-      <c r="AY4" t="n" s="0">
-        <v>11000.0</v>
-      </c>
-      <c r="AZ4" t="n" s="0">
-        <v>84500.0</v>
       </c>
     </row>
     <row r="5">
@@ -1189,154 +1189,154 @@
         <v>100.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>64400.0</v>
+        <v>40600.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>48700.0</v>
+        <v>39200.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>40200.0</v>
+        <v>48000.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>36600.0</v>
+        <v>57800.0</v>
       </c>
       <c r="G5" t="n" s="0">
-        <v>38300.0</v>
+        <v>49400.0</v>
       </c>
       <c r="H5" t="n" s="0">
-        <v>40000.0</v>
+        <v>49800.0</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>57200.0</v>
+        <v>46300.0</v>
       </c>
       <c r="J5" t="n" s="0">
-        <v>100300.0</v>
+        <v>67300.0</v>
       </c>
       <c r="K5" t="n" s="0">
-        <v>65000.0</v>
+        <v>56100.0</v>
       </c>
       <c r="L5" t="n" s="0">
-        <v>59100.0</v>
+        <v>41300.0</v>
       </c>
       <c r="M5" t="n" s="0">
-        <v>40500.0</v>
+        <v>48000.0</v>
       </c>
       <c r="N5" t="n" s="0">
-        <v>39500.0</v>
+        <v>62300.0</v>
       </c>
       <c r="O5" t="n" s="0">
-        <v>58800.0</v>
+        <v>54800.0</v>
       </c>
       <c r="P5" t="n" s="0">
-        <v>40200.0</v>
+        <v>41400.0</v>
       </c>
       <c r="Q5" t="n" s="0">
-        <v>64600.0</v>
+        <v>37700.0</v>
       </c>
       <c r="R5" t="n" s="0">
-        <v>34000.0</v>
+        <v>57100.0</v>
       </c>
       <c r="S5" t="n" s="0">
-        <v>55900.0</v>
+        <v>35500.0</v>
       </c>
       <c r="T5" t="n" s="0">
-        <v>60600.0</v>
+        <v>37300.0</v>
       </c>
       <c r="U5" t="n" s="0">
-        <v>65900.0</v>
+        <v>55600.0</v>
       </c>
       <c r="V5" t="n" s="0">
-        <v>54700.0</v>
+        <v>59200.0</v>
       </c>
       <c r="W5" t="n" s="0">
-        <v>55800.0</v>
+        <v>46500.0</v>
       </c>
       <c r="X5" t="n" s="0">
-        <v>52400.0</v>
+        <v>64200.0</v>
       </c>
       <c r="Y5" t="n" s="0">
-        <v>57500.0</v>
+        <v>54500.0</v>
       </c>
       <c r="Z5" t="n" s="0">
-        <v>40000.0</v>
+        <v>62100.0</v>
       </c>
       <c r="AA5" t="n" s="0">
-        <v>42600.0</v>
+        <v>73800.0</v>
       </c>
       <c r="AB5" t="n" s="0">
-        <v>9900.0</v>
+        <v>47500.0</v>
       </c>
       <c r="AC5" t="n" s="0">
-        <v>10400.0</v>
+        <v>11800.0</v>
       </c>
       <c r="AD5" t="n" s="0">
-        <v>12200.0</v>
+        <v>5800.0</v>
       </c>
       <c r="AE5" t="n" s="0">
+        <v>8900.0</v>
+      </c>
+      <c r="AF5" t="n" s="0">
+        <v>10100.0</v>
+      </c>
+      <c r="AG5" t="n" s="0">
+        <v>10500.0</v>
+      </c>
+      <c r="AH5" t="n" s="0">
         <v>10600.0</v>
       </c>
-      <c r="AF5" t="n" s="0">
-        <v>9500.0</v>
-      </c>
-      <c r="AG5" t="n" s="0">
-        <v>9800.0</v>
-      </c>
-      <c r="AH5" t="n" s="0">
-        <v>8800.0</v>
-      </c>
       <c r="AI5" t="n" s="0">
-        <v>5200.0</v>
+        <v>10100.0</v>
       </c>
       <c r="AJ5" t="n" s="0">
-        <v>9800.0</v>
+        <v>12800.0</v>
       </c>
       <c r="AK5" t="n" s="0">
-        <v>10900.0</v>
+        <v>12400.0</v>
       </c>
       <c r="AL5" t="n" s="0">
-        <v>10700.0</v>
+        <v>7100.0</v>
       </c>
       <c r="AM5" t="n" s="0">
         <v>9300.0</v>
       </c>
       <c r="AN5" t="n" s="0">
-        <v>9800.0</v>
+        <v>7700.0</v>
       </c>
       <c r="AO5" t="n" s="0">
-        <v>10400.0</v>
+        <v>11300.0</v>
       </c>
       <c r="AP5" t="n" s="0">
-        <v>10300.0</v>
+        <v>8700.0</v>
       </c>
       <c r="AQ5" t="n" s="0">
-        <v>10300.0</v>
+        <v>11000.0</v>
       </c>
       <c r="AR5" t="n" s="0">
-        <v>9700.0</v>
+        <v>11300.0</v>
       </c>
       <c r="AS5" t="n" s="0">
-        <v>10400.0</v>
+        <v>11600.0</v>
       </c>
       <c r="AT5" t="n" s="0">
-        <v>10300.0</v>
+        <v>17000.0</v>
       </c>
       <c r="AU5" t="n" s="0">
-        <v>5300.0</v>
+        <v>9400.0</v>
       </c>
       <c r="AV5" t="n" s="0">
-        <v>7900.0</v>
+        <v>11700.0</v>
       </c>
       <c r="AW5" t="n" s="0">
-        <v>12600.0</v>
+        <v>63000.0</v>
       </c>
       <c r="AX5" t="n" s="0">
-        <v>10900.0</v>
+        <v>61400.0</v>
       </c>
       <c r="AY5" t="n" s="0">
-        <v>10700.0</v>
+        <v>30300.0</v>
       </c>
       <c r="AZ5" t="n" s="0">
-        <v>38800.0</v>
+        <v>3500.0</v>
       </c>
     </row>
     <row r="6">
@@ -1347,154 +1347,154 @@
         <v>100.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>92200.0</v>
+        <v>46400.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>54500.0</v>
+        <v>56000.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>46400.0</v>
+        <v>46000.0</v>
       </c>
       <c r="F6" t="n" s="0">
+        <v>93300.0</v>
+      </c>
+      <c r="G6" t="n" s="0">
+        <v>76400.0</v>
+      </c>
+      <c r="H6" t="n" s="0">
         <v>45100.0</v>
       </c>
-      <c r="G6" t="n" s="0">
-        <v>47000.0</v>
-      </c>
-      <c r="H6" t="n" s="0">
-        <v>46100.0</v>
-      </c>
       <c r="I6" t="n" s="0">
-        <v>89100.0</v>
+        <v>81100.0</v>
       </c>
       <c r="J6" t="n" s="0">
-        <v>100200.0</v>
+        <v>93900.0</v>
       </c>
       <c r="K6" t="n" s="0">
-        <v>95200.0</v>
+        <v>84600.0</v>
       </c>
       <c r="L6" t="n" s="0">
-        <v>87300.0</v>
+        <v>52000.0</v>
       </c>
       <c r="M6" t="n" s="0">
-        <v>47100.0</v>
+        <v>78900.0</v>
       </c>
       <c r="N6" t="n" s="0">
-        <v>50200.0</v>
+        <v>104200.0</v>
       </c>
       <c r="O6" t="n" s="0">
-        <v>45300.0</v>
+        <v>47200.0</v>
       </c>
       <c r="P6" t="n" s="0">
-        <v>13400.0</v>
+        <v>20700.0</v>
       </c>
       <c r="Q6" t="n" s="0">
-        <v>22100.0</v>
+        <v>11600.0</v>
       </c>
       <c r="R6" t="n" s="0">
-        <v>12500.0</v>
+        <v>22300.0</v>
       </c>
       <c r="S6" t="n" s="0">
-        <v>21700.0</v>
+        <v>13000.0</v>
       </c>
       <c r="T6" t="n" s="0">
-        <v>20500.0</v>
+        <v>13200.0</v>
       </c>
       <c r="U6" t="n" s="0">
-        <v>21300.0</v>
+        <v>23600.0</v>
       </c>
       <c r="V6" t="n" s="0">
-        <v>20800.0</v>
+        <v>22800.0</v>
       </c>
       <c r="W6" t="n" s="0">
-        <v>22000.0</v>
+        <v>22500.0</v>
       </c>
       <c r="X6" t="n" s="0">
-        <v>21800.0</v>
+        <v>23100.0</v>
       </c>
       <c r="Y6" t="n" s="0">
-        <v>21300.0</v>
+        <v>22300.0</v>
       </c>
       <c r="Z6" t="n" s="0">
-        <v>18400.0</v>
+        <v>33500.0</v>
       </c>
       <c r="AA6" t="n" s="0">
-        <v>63200.0</v>
+        <v>76400.0</v>
       </c>
       <c r="AB6" t="n" s="0">
-        <v>21600.0</v>
+        <v>22200.0</v>
       </c>
       <c r="AC6" t="n" s="0">
-        <v>10300.0</v>
+        <v>10000.0</v>
       </c>
       <c r="AD6" t="n" s="0">
-        <v>8700.0</v>
+        <v>6700.0</v>
       </c>
       <c r="AE6" t="n" s="0">
+        <v>6800.0</v>
+      </c>
+      <c r="AF6" t="n" s="0">
+        <v>8000.0</v>
+      </c>
+      <c r="AG6" t="n" s="0">
+        <v>8400.0</v>
+      </c>
+      <c r="AH6" t="n" s="0">
+        <v>6300.0</v>
+      </c>
+      <c r="AI6" t="n" s="0">
+        <v>8400.0</v>
+      </c>
+      <c r="AJ6" t="n" s="0">
+        <v>8200.0</v>
+      </c>
+      <c r="AK6" t="n" s="0">
+        <v>6800.0</v>
+      </c>
+      <c r="AL6" t="n" s="0">
+        <v>7900.0</v>
+      </c>
+      <c r="AM6" t="n" s="0">
+        <v>11100.0</v>
+      </c>
+      <c r="AN6" t="n" s="0">
+        <v>6800.0</v>
+      </c>
+      <c r="AO6" t="n" s="0">
+        <v>8100.0</v>
+      </c>
+      <c r="AP6" t="n" s="0">
+        <v>8600.0</v>
+      </c>
+      <c r="AQ6" t="n" s="0">
+        <v>8600.0</v>
+      </c>
+      <c r="AR6" t="n" s="0">
+        <v>8800.0</v>
+      </c>
+      <c r="AS6" t="n" s="0">
+        <v>8800.0</v>
+      </c>
+      <c r="AT6" t="n" s="0">
         <v>8500.0</v>
       </c>
-      <c r="AF6" t="n" s="0">
-        <v>8100.0</v>
-      </c>
-      <c r="AG6" t="n" s="0">
-        <v>8200.0</v>
-      </c>
-      <c r="AH6" t="n" s="0">
-        <v>8100.0</v>
-      </c>
-      <c r="AI6" t="n" s="0">
-        <v>6100.0</v>
-      </c>
-      <c r="AJ6" t="n" s="0">
+      <c r="AU6" t="n" s="0">
+        <v>8500.0</v>
+      </c>
+      <c r="AV6" t="n" s="0">
+        <v>8500.0</v>
+      </c>
+      <c r="AW6" t="n" s="0">
+        <v>8500.0</v>
+      </c>
+      <c r="AX6" t="n" s="0">
+        <v>8800.0</v>
+      </c>
+      <c r="AY6" t="n" s="0">
         <v>8900.0</v>
       </c>
-      <c r="AK6" t="n" s="0">
-        <v>8300.0</v>
-      </c>
-      <c r="AL6" t="n" s="0">
-        <v>8700.0</v>
-      </c>
-      <c r="AM6" t="n" s="0">
-        <v>8300.0</v>
-      </c>
-      <c r="AN6" t="n" s="0">
-        <v>8200.0</v>
-      </c>
-      <c r="AO6" t="n" s="0">
-        <v>8500.0</v>
-      </c>
-      <c r="AP6" t="n" s="0">
-        <v>8400.0</v>
-      </c>
-      <c r="AQ6" t="n" s="0">
-        <v>8400.0</v>
-      </c>
-      <c r="AR6" t="n" s="0">
-        <v>8500.0</v>
-      </c>
-      <c r="AS6" t="n" s="0">
-        <v>8700.0</v>
-      </c>
-      <c r="AT6" t="n" s="0">
-        <v>8300.0</v>
-      </c>
-      <c r="AU6" t="n" s="0">
-        <v>6300.0</v>
-      </c>
-      <c r="AV6" t="n" s="0">
-        <v>8200.0</v>
-      </c>
-      <c r="AW6" t="n" s="0">
-        <v>7800.0</v>
-      </c>
-      <c r="AX6" t="n" s="0">
-        <v>8300.0</v>
-      </c>
-      <c r="AY6" t="n" s="0">
-        <v>8300.0</v>
-      </c>
       <c r="AZ6" t="n" s="0">
-        <v>9200.0</v>
+        <v>8600.0</v>
       </c>
     </row>
     <row r="7">
@@ -1505,154 +1505,154 @@
         <v>100.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>60500.0</v>
+        <v>47000.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>53000.0</v>
+        <v>59700.0</v>
       </c>
       <c r="E7" t="n" s="0">
-        <v>45100.0</v>
+        <v>46100.0</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>44100.0</v>
+        <v>97100.0</v>
       </c>
       <c r="G7" t="n" s="0">
-        <v>46100.0</v>
+        <v>76300.0</v>
       </c>
       <c r="H7" t="n" s="0">
-        <v>44600.0</v>
+        <v>71400.0</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>86200.0</v>
+        <v>80300.0</v>
       </c>
       <c r="J7" t="n" s="0">
-        <v>102500.0</v>
+        <v>99700.0</v>
       </c>
       <c r="K7" t="n" s="0">
-        <v>88200.0</v>
+        <v>93100.0</v>
       </c>
       <c r="L7" t="n" s="0">
-        <v>94100.0</v>
+        <v>50200.0</v>
       </c>
       <c r="M7" t="n" s="0">
-        <v>46000.0</v>
+        <v>76000.0</v>
       </c>
       <c r="N7" t="n" s="0">
-        <v>48400.0</v>
+        <v>97500.0</v>
       </c>
       <c r="O7" t="n" s="0">
-        <v>47400.0</v>
+        <v>37600.0</v>
       </c>
       <c r="P7" t="n" s="0">
-        <v>12600.0</v>
+        <v>16100.0</v>
       </c>
       <c r="Q7" t="n" s="0">
-        <v>21400.0</v>
+        <v>11100.0</v>
       </c>
       <c r="R7" t="n" s="0">
+        <v>22600.0</v>
+      </c>
+      <c r="S7" t="n" s="0">
+        <v>11200.0</v>
+      </c>
+      <c r="T7" t="n" s="0">
         <v>11300.0</v>
       </c>
-      <c r="S7" t="n" s="0">
-        <v>26400.0</v>
-      </c>
-      <c r="T7" t="n" s="0">
-        <v>21100.0</v>
-      </c>
       <c r="U7" t="n" s="0">
-        <v>21900.0</v>
+        <v>23000.0</v>
       </c>
       <c r="V7" t="n" s="0">
-        <v>21000.0</v>
+        <v>22700.0</v>
       </c>
       <c r="W7" t="n" s="0">
-        <v>22300.0</v>
+        <v>21600.0</v>
       </c>
       <c r="X7" t="n" s="0">
-        <v>21700.0</v>
+        <v>34900.0</v>
       </c>
       <c r="Y7" t="n" s="0">
-        <v>21200.0</v>
+        <v>22500.0</v>
       </c>
       <c r="Z7" t="n" s="0">
-        <v>15500.0</v>
+        <v>66100.0</v>
       </c>
       <c r="AA7" t="n" s="0">
-        <v>23800.0</v>
+        <v>17600.0</v>
       </c>
       <c r="AB7" t="n" s="0">
-        <v>21500.0</v>
+        <v>10100.0</v>
       </c>
       <c r="AC7" t="n" s="0">
-        <v>82700.0</v>
+        <v>9000.0</v>
       </c>
       <c r="AD7" t="n" s="0">
-        <v>23100.0</v>
+        <v>5500.0</v>
       </c>
       <c r="AE7" t="n" s="0">
-        <v>11400.0</v>
+        <v>6900.0</v>
       </c>
       <c r="AF7" t="n" s="0">
+        <v>7900.0</v>
+      </c>
+      <c r="AG7" t="n" s="0">
+        <v>8300.0</v>
+      </c>
+      <c r="AH7" t="n" s="0">
+        <v>5800.0</v>
+      </c>
+      <c r="AI7" t="n" s="0">
+        <v>8000.0</v>
+      </c>
+      <c r="AJ7" t="n" s="0">
+        <v>8800.0</v>
+      </c>
+      <c r="AK7" t="n" s="0">
+        <v>7200.0</v>
+      </c>
+      <c r="AL7" t="n" s="0">
+        <v>6500.0</v>
+      </c>
+      <c r="AM7" t="n" s="0">
+        <v>11000.0</v>
+      </c>
+      <c r="AN7" t="n" s="0">
+        <v>6000.0</v>
+      </c>
+      <c r="AO7" t="n" s="0">
         <v>8500.0</v>
       </c>
-      <c r="AG7" t="n" s="0">
-        <v>7700.0</v>
-      </c>
-      <c r="AH7" t="n" s="0">
+      <c r="AP7" t="n" s="0">
+        <v>8400.0</v>
+      </c>
+      <c r="AQ7" t="n" s="0">
         <v>8000.0</v>
-      </c>
-      <c r="AI7" t="n" s="0">
-        <v>5800.0</v>
-      </c>
-      <c r="AJ7" t="n" s="0">
-        <v>8000.0</v>
-      </c>
-      <c r="AK7" t="n" s="0">
-        <v>8500.0</v>
-      </c>
-      <c r="AL7" t="n" s="0">
-        <v>8600.0</v>
-      </c>
-      <c r="AM7" t="n" s="0">
-        <v>8000.0</v>
-      </c>
-      <c r="AN7" t="n" s="0">
-        <v>8400.0</v>
-      </c>
-      <c r="AO7" t="n" s="0">
-        <v>8100.0</v>
-      </c>
-      <c r="AP7" t="n" s="0">
-        <v>8300.0</v>
-      </c>
-      <c r="AQ7" t="n" s="0">
-        <v>7100.0</v>
       </c>
       <c r="AR7" t="n" s="0">
         <v>8300.0</v>
       </c>
       <c r="AS7" t="n" s="0">
-        <v>8100.0</v>
+        <v>9100.0</v>
       </c>
       <c r="AT7" t="n" s="0">
-        <v>8100.0</v>
+        <v>8300.0</v>
       </c>
       <c r="AU7" t="n" s="0">
-        <v>5700.0</v>
+        <v>15300.0</v>
       </c>
       <c r="AV7" t="n" s="0">
         <v>8400.0</v>
       </c>
       <c r="AW7" t="n" s="0">
+        <v>8400.0</v>
+      </c>
+      <c r="AX7" t="n" s="0">
         <v>9000.0</v>
       </c>
-      <c r="AX7" t="n" s="0">
+      <c r="AY7" t="n" s="0">
+        <v>8300.0</v>
+      </c>
+      <c r="AZ7" t="n" s="0">
         <v>8400.0</v>
-      </c>
-      <c r="AY7" t="n" s="0">
-        <v>8700.0</v>
-      </c>
-      <c r="AZ7" t="n" s="0">
-        <v>9000.0</v>
       </c>
     </row>
     <row r="8">
@@ -1663,154 +1663,154 @@
         <v>100.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>45600.0</v>
+        <v>44700.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>80100.0</v>
+        <v>84200.0</v>
       </c>
       <c r="E8" t="n" s="0">
-        <v>32900.0</v>
+        <v>35400.0</v>
       </c>
       <c r="F8" t="n" s="0">
-        <v>66200.0</v>
+        <v>67200.0</v>
       </c>
       <c r="G8" t="n" s="0">
+        <v>24500.0</v>
+      </c>
+      <c r="H8" t="n" s="0">
+        <v>9900.0</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>15300.0</v>
+      </c>
+      <c r="J8" t="n" s="0">
+        <v>20600.0</v>
+      </c>
+      <c r="K8" t="n" s="0">
+        <v>16800.0</v>
+      </c>
+      <c r="L8" t="n" s="0">
+        <v>10500.0</v>
+      </c>
+      <c r="M8" t="n" s="0">
+        <v>14100.0</v>
+      </c>
+      <c r="N8" t="n" s="0">
+        <v>18000.0</v>
+      </c>
+      <c r="O8" t="n" s="0">
+        <v>15200.0</v>
+      </c>
+      <c r="P8" t="n" s="0">
+        <v>13200.0</v>
+      </c>
+      <c r="Q8" t="n" s="0">
+        <v>10100.0</v>
+      </c>
+      <c r="R8" t="n" s="0">
+        <v>17100.0</v>
+      </c>
+      <c r="S8" t="n" s="0">
+        <v>17400.0</v>
+      </c>
+      <c r="T8" t="n" s="0">
+        <v>9900.0</v>
+      </c>
+      <c r="U8" t="n" s="0">
+        <v>17900.0</v>
+      </c>
+      <c r="V8" t="n" s="0">
+        <v>17200.0</v>
+      </c>
+      <c r="W8" t="n" s="0">
+        <v>14200.0</v>
+      </c>
+      <c r="X8" t="n" s="0">
+        <v>18900.0</v>
+      </c>
+      <c r="Y8" t="n" s="0">
+        <v>30100.0</v>
+      </c>
+      <c r="Z8" t="n" s="0">
+        <v>16300.0</v>
+      </c>
+      <c r="AA8" t="n" s="0">
+        <v>31900.0</v>
+      </c>
+      <c r="AB8" t="n" s="0">
+        <v>19600.0</v>
+      </c>
+      <c r="AC8" t="n" s="0">
+        <v>14500.0</v>
+      </c>
+      <c r="AD8" t="n" s="0">
+        <v>10500.0</v>
+      </c>
+      <c r="AE8" t="n" s="0">
+        <v>12300.0</v>
+      </c>
+      <c r="AF8" t="n" s="0">
+        <v>12900.0</v>
+      </c>
+      <c r="AG8" t="n" s="0">
+        <v>13400.0</v>
+      </c>
+      <c r="AH8" t="n" s="0">
+        <v>10600.0</v>
+      </c>
+      <c r="AI8" t="n" s="0">
+        <v>15400.0</v>
+      </c>
+      <c r="AJ8" t="n" s="0">
+        <v>13600.0</v>
+      </c>
+      <c r="AK8" t="n" s="0">
+        <v>10100.0</v>
+      </c>
+      <c r="AL8" t="n" s="0">
+        <v>11100.0</v>
+      </c>
+      <c r="AM8" t="n" s="0">
+        <v>54400.0</v>
+      </c>
+      <c r="AN8" t="n" s="0">
+        <v>10000.0</v>
+      </c>
+      <c r="AO8" t="n" s="0">
+        <v>12400.0</v>
+      </c>
+      <c r="AP8" t="n" s="0">
+        <v>12000.0</v>
+      </c>
+      <c r="AQ8" t="n" s="0">
+        <v>12000.0</v>
+      </c>
+      <c r="AR8" t="n" s="0">
+        <v>14200.0</v>
+      </c>
+      <c r="AS8" t="n" s="0">
+        <v>12500.0</v>
+      </c>
+      <c r="AT8" t="n" s="0">
+        <v>12000.0</v>
+      </c>
+      <c r="AU8" t="n" s="0">
+        <v>13000.0</v>
+      </c>
+      <c r="AV8" t="n" s="0">
+        <v>12400.0</v>
+      </c>
+      <c r="AW8" t="n" s="0">
+        <v>12800.0</v>
+      </c>
+      <c r="AX8" t="n" s="0">
+        <v>17200.0</v>
+      </c>
+      <c r="AY8" t="n" s="0">
         <v>23400.0</v>
       </c>
-      <c r="H8" t="n" s="0">
-        <v>15400.0</v>
-      </c>
-      <c r="I8" t="n" s="0">
-        <v>15900.0</v>
-      </c>
-      <c r="J8" t="n" s="0">
-        <v>26500.0</v>
-      </c>
-      <c r="K8" t="n" s="0">
-        <v>17800.0</v>
-      </c>
-      <c r="L8" t="n" s="0">
-        <v>16300.0</v>
-      </c>
-      <c r="M8" t="n" s="0">
-        <v>9700.0</v>
-      </c>
-      <c r="N8" t="n" s="0">
-        <v>16700.0</v>
-      </c>
-      <c r="O8" t="n" s="0">
-        <v>17400.0</v>
-      </c>
-      <c r="P8" t="n" s="0">
-        <v>9900.0</v>
-      </c>
-      <c r="Q8" t="n" s="0">
-        <v>18000.0</v>
-      </c>
-      <c r="R8" t="n" s="0">
-        <v>9700.0</v>
-      </c>
-      <c r="S8" t="n" s="0">
-        <v>17200.0</v>
-      </c>
-      <c r="T8" t="n" s="0">
-        <v>15500.0</v>
-      </c>
-      <c r="U8" t="n" s="0">
-        <v>14800.0</v>
-      </c>
-      <c r="V8" t="n" s="0">
-        <v>14400.0</v>
-      </c>
-      <c r="W8" t="n" s="0">
-        <v>16200.0</v>
-      </c>
-      <c r="X8" t="n" s="0">
-        <v>15800.0</v>
-      </c>
-      <c r="Y8" t="n" s="0">
-        <v>144500.0</v>
-      </c>
-      <c r="Z8" t="n" s="0">
-        <v>9700.0</v>
-      </c>
-      <c r="AA8" t="n" s="0">
-        <v>33700.0</v>
-      </c>
-      <c r="AB8" t="n" s="0">
-        <v>14600.0</v>
-      </c>
-      <c r="AC8" t="n" s="0">
-        <v>14100.0</v>
-      </c>
-      <c r="AD8" t="n" s="0">
-        <v>15600.0</v>
-      </c>
-      <c r="AE8" t="n" s="0">
-        <v>12000.0</v>
-      </c>
-      <c r="AF8" t="n" s="0">
-        <v>13300.0</v>
-      </c>
-      <c r="AG8" t="n" s="0">
-        <v>12900.0</v>
-      </c>
-      <c r="AH8" t="n" s="0">
-        <v>12500.0</v>
-      </c>
-      <c r="AI8" t="n" s="0">
-        <v>29500.0</v>
-      </c>
-      <c r="AJ8" t="n" s="0">
-        <v>12600.0</v>
-      </c>
-      <c r="AK8" t="n" s="0">
-        <v>13200.0</v>
-      </c>
-      <c r="AL8" t="n" s="0">
-        <v>13300.0</v>
-      </c>
-      <c r="AM8" t="n" s="0">
-        <v>12200.0</v>
-      </c>
-      <c r="AN8" t="n" s="0">
-        <v>12600.0</v>
-      </c>
-      <c r="AO8" t="n" s="0">
-        <v>16200.0</v>
-      </c>
-      <c r="AP8" t="n" s="0">
-        <v>12300.0</v>
-      </c>
-      <c r="AQ8" t="n" s="0">
-        <v>12300.0</v>
-      </c>
-      <c r="AR8" t="n" s="0">
-        <v>12000.0</v>
-      </c>
-      <c r="AS8" t="n" s="0">
+      <c r="AZ8" t="n" s="0">
         <v>11900.0</v>
-      </c>
-      <c r="AT8" t="n" s="0">
-        <v>11300.0</v>
-      </c>
-      <c r="AU8" t="n" s="0">
-        <v>9700.0</v>
-      </c>
-      <c r="AV8" t="n" s="0">
-        <v>12100.0</v>
-      </c>
-      <c r="AW8" t="n" s="0">
-        <v>11500.0</v>
-      </c>
-      <c r="AX8" t="n" s="0">
-        <v>12500.0</v>
-      </c>
-      <c r="AY8" t="n" s="0">
-        <v>12100.0</v>
-      </c>
-      <c r="AZ8" t="n" s="0">
-        <v>16700.0</v>
       </c>
     </row>
     <row r="9">
@@ -1821,154 +1821,154 @@
         <v>100.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>42200.0</v>
+        <v>42700.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>68000.0</v>
+        <v>87800.0</v>
       </c>
       <c r="E9" t="n" s="0">
-        <v>152700.0</v>
+        <v>72300.0</v>
       </c>
       <c r="F9" t="n" s="0">
-        <v>28700.0</v>
+        <v>74000.0</v>
       </c>
       <c r="G9" t="n" s="0">
-        <v>15400.0</v>
+        <v>28500.0</v>
       </c>
       <c r="H9" t="n" s="0">
-        <v>9200.0</v>
+        <v>9300.0</v>
       </c>
       <c r="I9" t="n" s="0">
-        <v>26400.0</v>
+        <v>14300.0</v>
       </c>
       <c r="J9" t="n" s="0">
-        <v>19700.0</v>
+        <v>17800.0</v>
       </c>
       <c r="K9" t="n" s="0">
         <v>16600.0</v>
       </c>
       <c r="L9" t="n" s="0">
-        <v>16700.0</v>
+        <v>10200.0</v>
       </c>
       <c r="M9" t="n" s="0">
-        <v>9000.0</v>
+        <v>14800.0</v>
       </c>
       <c r="N9" t="n" s="0">
-        <v>8800.0</v>
+        <v>16800.0</v>
       </c>
       <c r="O9" t="n" s="0">
-        <v>17400.0</v>
+        <v>14000.0</v>
       </c>
       <c r="P9" t="n" s="0">
+        <v>21000.0</v>
+      </c>
+      <c r="Q9" t="n" s="0">
+        <v>9600.0</v>
+      </c>
+      <c r="R9" t="n" s="0">
+        <v>17900.0</v>
+      </c>
+      <c r="S9" t="n" s="0">
         <v>9300.0</v>
       </c>
-      <c r="Q9" t="n" s="0">
-        <v>17400.0</v>
-      </c>
-      <c r="R9" t="n" s="0">
-        <v>9200.0</v>
-      </c>
-      <c r="S9" t="n" s="0">
+      <c r="T9" t="n" s="0">
+        <v>8900.0</v>
+      </c>
+      <c r="U9" t="n" s="0">
+        <v>17300.0</v>
+      </c>
+      <c r="V9" t="n" s="0">
+        <v>20400.0</v>
+      </c>
+      <c r="W9" t="n" s="0">
+        <v>14300.0</v>
+      </c>
+      <c r="X9" t="n" s="0">
+        <v>18300.0</v>
+      </c>
+      <c r="Y9" t="n" s="0">
+        <v>20300.0</v>
+      </c>
+      <c r="Z9" t="n" s="0">
+        <v>17100.0</v>
+      </c>
+      <c r="AA9" t="n" s="0">
+        <v>13800.0</v>
+      </c>
+      <c r="AB9" t="n" s="0">
+        <v>26000.0</v>
+      </c>
+      <c r="AC9" t="n" s="0">
+        <v>23100.0</v>
+      </c>
+      <c r="AD9" t="n" s="0">
+        <v>10300.0</v>
+      </c>
+      <c r="AE9" t="n" s="0">
+        <v>14800.0</v>
+      </c>
+      <c r="AF9" t="n" s="0">
         <v>16900.0</v>
       </c>
-      <c r="T9" t="n" s="0">
+      <c r="AG9" t="n" s="0">
         <v>17200.0</v>
       </c>
-      <c r="U9" t="n" s="0">
-        <v>15100.0</v>
-      </c>
-      <c r="V9" t="n" s="0">
-        <v>14600.0</v>
-      </c>
-      <c r="W9" t="n" s="0">
+      <c r="AH9" t="n" s="0">
+        <v>8900.0</v>
+      </c>
+      <c r="AI9" t="n" s="0">
+        <v>32200.0</v>
+      </c>
+      <c r="AJ9" t="n" s="0">
+        <v>22900.0</v>
+      </c>
+      <c r="AK9" t="n" s="0">
+        <v>14100.0</v>
+      </c>
+      <c r="AL9" t="n" s="0">
         <v>15800.0</v>
       </c>
-      <c r="X9" t="n" s="0">
-        <v>17400.0</v>
-      </c>
-      <c r="Y9" t="n" s="0">
-        <v>123800.0</v>
-      </c>
-      <c r="Z9" t="n" s="0">
-        <v>10500.0</v>
-      </c>
-      <c r="AA9" t="n" s="0">
-        <v>16900.0</v>
-      </c>
-      <c r="AB9" t="n" s="0">
-        <v>14900.0</v>
-      </c>
-      <c r="AC9" t="n" s="0">
-        <v>18100.0</v>
-      </c>
-      <c r="AD9" t="n" s="0">
-        <v>29100.0</v>
-      </c>
-      <c r="AE9" t="n" s="0">
+      <c r="AM9" t="n" s="0">
+        <v>24300.0</v>
+      </c>
+      <c r="AN9" t="n" s="0">
+        <v>8400.0</v>
+      </c>
+      <c r="AO9" t="n" s="0">
         <v>12100.0</v>
       </c>
-      <c r="AF9" t="n" s="0">
-        <v>13200.0</v>
-      </c>
-      <c r="AG9" t="n" s="0">
-        <v>13700.0</v>
-      </c>
-      <c r="AH9" t="n" s="0">
-        <v>15400.0</v>
-      </c>
-      <c r="AI9" t="n" s="0">
-        <v>8300.0</v>
-      </c>
-      <c r="AJ9" t="n" s="0">
-        <v>30100.0</v>
-      </c>
-      <c r="AK9" t="n" s="0">
+      <c r="AP9" t="n" s="0">
+        <v>11500.0</v>
+      </c>
+      <c r="AQ9" t="n" s="0">
+        <v>11700.0</v>
+      </c>
+      <c r="AR9" t="n" s="0">
+        <v>13400.0</v>
+      </c>
+      <c r="AS9" t="n" s="0">
+        <v>12400.0</v>
+      </c>
+      <c r="AT9" t="n" s="0">
+        <v>11900.0</v>
+      </c>
+      <c r="AU9" t="n" s="0">
+        <v>11200.0</v>
+      </c>
+      <c r="AV9" t="n" s="0">
+        <v>12800.0</v>
+      </c>
+      <c r="AW9" t="n" s="0">
         <v>12300.0</v>
       </c>
-      <c r="AL9" t="n" s="0">
+      <c r="AX9" t="n" s="0">
+        <v>12300.0</v>
+      </c>
+      <c r="AY9" t="n" s="0">
         <v>13500.0</v>
       </c>
-      <c r="AM9" t="n" s="0">
-        <v>11700.0</v>
-      </c>
-      <c r="AN9" t="n" s="0">
+      <c r="AZ9" t="n" s="0">
         <v>11800.0</v>
-      </c>
-      <c r="AO9" t="n" s="0">
-        <v>11500.0</v>
-      </c>
-      <c r="AP9" t="n" s="0">
-        <v>12500.0</v>
-      </c>
-      <c r="AQ9" t="n" s="0">
-        <v>11800.0</v>
-      </c>
-      <c r="AR9" t="n" s="0">
-        <v>11600.0</v>
-      </c>
-      <c r="AS9" t="n" s="0">
-        <v>12800.0</v>
-      </c>
-      <c r="AT9" t="n" s="0">
-        <v>13600.0</v>
-      </c>
-      <c r="AU9" t="n" s="0">
-        <v>8800.0</v>
-      </c>
-      <c r="AV9" t="n" s="0">
-        <v>11500.0</v>
-      </c>
-      <c r="AW9" t="n" s="0">
-        <v>11200.0</v>
-      </c>
-      <c r="AX9" t="n" s="0">
-        <v>18200.0</v>
-      </c>
-      <c r="AY9" t="n" s="0">
-        <v>11700.0</v>
-      </c>
-      <c r="AZ9" t="n" s="0">
-        <v>14200.0</v>
       </c>
     </row>
     <row r="10">
@@ -1979,154 +1979,154 @@
         <v>100.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>41300.0</v>
+        <v>70000.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>49900.0</v>
+        <v>117400.0</v>
       </c>
       <c r="E10" t="n" s="0">
-        <v>66700.0</v>
+        <v>75300.0</v>
       </c>
       <c r="F10" t="n" s="0">
-        <v>35400.0</v>
+        <v>43100.0</v>
       </c>
       <c r="G10" t="n" s="0">
-        <v>18200.0</v>
+        <v>23900.0</v>
       </c>
       <c r="H10" t="n" s="0">
-        <v>23600.0</v>
+        <v>30500.0</v>
       </c>
       <c r="I10" t="n" s="0">
-        <v>32500.0</v>
+        <v>29500.0</v>
       </c>
       <c r="J10" t="n" s="0">
+        <v>18300.0</v>
+      </c>
+      <c r="K10" t="n" s="0">
+        <v>16300.0</v>
+      </c>
+      <c r="L10" t="n" s="0">
+        <v>13500.0</v>
+      </c>
+      <c r="M10" t="n" s="0">
+        <v>15000.0</v>
+      </c>
+      <c r="N10" t="n" s="0">
+        <v>15300.0</v>
+      </c>
+      <c r="O10" t="n" s="0">
+        <v>16400.0</v>
+      </c>
+      <c r="P10" t="n" s="0">
+        <v>17000.0</v>
+      </c>
+      <c r="Q10" t="n" s="0">
+        <v>10500.0</v>
+      </c>
+      <c r="R10" t="n" s="0">
+        <v>18400.0</v>
+      </c>
+      <c r="S10" t="n" s="0">
+        <v>10400.0</v>
+      </c>
+      <c r="T10" t="n" s="0">
+        <v>25500.0</v>
+      </c>
+      <c r="U10" t="n" s="0">
+        <v>16300.0</v>
+      </c>
+      <c r="V10" t="n" s="0">
+        <v>17400.0</v>
+      </c>
+      <c r="W10" t="n" s="0">
+        <v>15600.0</v>
+      </c>
+      <c r="X10" t="n" s="0">
+        <v>15800.0</v>
+      </c>
+      <c r="Y10" t="n" s="0">
+        <v>15100.0</v>
+      </c>
+      <c r="Z10" t="n" s="0">
+        <v>19100.0</v>
+      </c>
+      <c r="AA10" t="n" s="0">
         <v>19300.0</v>
       </c>
-      <c r="K10" t="n" s="0">
-        <v>17700.0</v>
-      </c>
-      <c r="L10" t="n" s="0">
-        <v>19800.0</v>
-      </c>
-      <c r="M10" t="n" s="0">
+      <c r="AB10" t="n" s="0">
+        <v>18100.0</v>
+      </c>
+      <c r="AC10" t="n" s="0">
+        <v>39300.0</v>
+      </c>
+      <c r="AD10" t="n" s="0">
+        <v>17200.0</v>
+      </c>
+      <c r="AE10" t="n" s="0">
+        <v>14600.0</v>
+      </c>
+      <c r="AF10" t="n" s="0">
+        <v>17000.0</v>
+      </c>
+      <c r="AG10" t="n" s="0">
+        <v>22400.0</v>
+      </c>
+      <c r="AH10" t="n" s="0">
+        <v>11400.0</v>
+      </c>
+      <c r="AI10" t="n" s="0">
+        <v>16500.0</v>
+      </c>
+      <c r="AJ10" t="n" s="0">
+        <v>18100.0</v>
+      </c>
+      <c r="AK10" t="n" s="0">
+        <v>48900.0</v>
+      </c>
+      <c r="AL10" t="n" s="0">
+        <v>14500.0</v>
+      </c>
+      <c r="AM10" t="n" s="0">
+        <v>21500.0</v>
+      </c>
+      <c r="AN10" t="n" s="0">
         <v>10900.0</v>
       </c>
-      <c r="N10" t="n" s="0">
-        <v>10800.0</v>
-      </c>
-      <c r="O10" t="n" s="0">
-        <v>17800.0</v>
-      </c>
-      <c r="P10" t="n" s="0">
-        <v>10700.0</v>
-      </c>
-      <c r="Q10" t="n" s="0">
-        <v>14900.0</v>
-      </c>
-      <c r="R10" t="n" s="0">
+      <c r="AO10" t="n" s="0">
         <v>16700.0</v>
       </c>
-      <c r="S10" t="n" s="0">
-        <v>16100.0</v>
-      </c>
-      <c r="T10" t="n" s="0">
-        <v>32300.0</v>
-      </c>
-      <c r="U10" t="n" s="0">
-        <v>23900.0</v>
-      </c>
-      <c r="V10" t="n" s="0">
-        <v>15800.0</v>
-      </c>
-      <c r="W10" t="n" s="0">
-        <v>17900.0</v>
-      </c>
-      <c r="X10" t="n" s="0">
-        <v>16400.0</v>
-      </c>
-      <c r="Y10" t="n" s="0">
-        <v>25000.0</v>
-      </c>
-      <c r="Z10" t="n" s="0">
-        <v>11300.0</v>
-      </c>
-      <c r="AA10" t="n" s="0">
-        <v>17200.0</v>
-      </c>
-      <c r="AB10" t="n" s="0">
-        <v>23000.0</v>
-      </c>
-      <c r="AC10" t="n" s="0">
+      <c r="AP10" t="n" s="0">
+        <v>13700.0</v>
+      </c>
+      <c r="AQ10" t="n" s="0">
+        <v>15400.0</v>
+      </c>
+      <c r="AR10" t="n" s="0">
+        <v>17100.0</v>
+      </c>
+      <c r="AS10" t="n" s="0">
+        <v>17500.0</v>
+      </c>
+      <c r="AT10" t="n" s="0">
         <v>16500.0</v>
       </c>
-      <c r="AD10" t="n" s="0">
-        <v>17300.0</v>
-      </c>
-      <c r="AE10" t="n" s="0">
-        <v>16200.0</v>
-      </c>
-      <c r="AF10" t="n" s="0">
-        <v>15400.0</v>
-      </c>
-      <c r="AG10" t="n" s="0">
-        <v>15900.0</v>
-      </c>
-      <c r="AH10" t="n" s="0">
-        <v>15300.0</v>
-      </c>
-      <c r="AI10" t="n" s="0">
-        <v>10300.0</v>
-      </c>
-      <c r="AJ10" t="n" s="0">
-        <v>16400.0</v>
-      </c>
-      <c r="AK10" t="n" s="0">
-        <v>28200.0</v>
-      </c>
-      <c r="AL10" t="n" s="0">
-        <v>21200.0</v>
-      </c>
-      <c r="AM10" t="n" s="0">
-        <v>16800.0</v>
-      </c>
-      <c r="AN10" t="n" s="0">
-        <v>13200.0</v>
-      </c>
-      <c r="AO10" t="n" s="0">
-        <v>15400.0</v>
-      </c>
-      <c r="AP10" t="n" s="0">
-        <v>15500.0</v>
-      </c>
-      <c r="AQ10" t="n" s="0">
-        <v>13600.0</v>
-      </c>
-      <c r="AR10" t="n" s="0">
-        <v>15300.0</v>
-      </c>
-      <c r="AS10" t="n" s="0">
-        <v>30900.0</v>
-      </c>
-      <c r="AT10" t="n" s="0">
+      <c r="AU10" t="n" s="0">
+        <v>15200.0</v>
+      </c>
+      <c r="AV10" t="n" s="0">
+        <v>18100.0</v>
+      </c>
+      <c r="AW10" t="n" s="0">
+        <v>46300.0</v>
+      </c>
+      <c r="AX10" t="n" s="0">
+        <v>16700.0</v>
+      </c>
+      <c r="AY10" t="n" s="0">
+        <v>36400.0</v>
+      </c>
+      <c r="AZ10" t="n" s="0">
         <v>15000.0</v>
-      </c>
-      <c r="AU10" t="n" s="0">
-        <v>10900.0</v>
-      </c>
-      <c r="AV10" t="n" s="0">
-        <v>16100.0</v>
-      </c>
-      <c r="AW10" t="n" s="0">
-        <v>16300.0</v>
-      </c>
-      <c r="AX10" t="n" s="0">
-        <v>16500.0</v>
-      </c>
-      <c r="AY10" t="n" s="0">
-        <v>15200.0</v>
-      </c>
-      <c r="AZ10" t="n" s="0">
-        <v>14200.0</v>
       </c>
     </row>
     <row r="11">
@@ -2137,154 +2137,154 @@
         <v>100.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>48800.0</v>
+        <v>41500.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>33400.0</v>
+        <v>36100.0</v>
       </c>
       <c r="E11" t="n" s="0">
-        <v>94000.0</v>
+        <v>76700.0</v>
       </c>
       <c r="F11" t="n" s="0">
-        <v>26200.0</v>
+        <v>26900.0</v>
       </c>
       <c r="G11" t="n" s="0">
-        <v>15400.0</v>
+        <v>273900.0</v>
       </c>
       <c r="H11" t="n" s="0">
-        <v>22700.0</v>
+        <v>21900.0</v>
       </c>
       <c r="I11" t="n" s="0">
-        <v>29000.0</v>
+        <v>27000.0</v>
       </c>
       <c r="J11" t="n" s="0">
-        <v>18600.0</v>
+        <v>19300.0</v>
       </c>
       <c r="K11" t="n" s="0">
-        <v>17500.0</v>
+        <v>15700.0</v>
       </c>
       <c r="L11" t="n" s="0">
+        <v>20600.0</v>
+      </c>
+      <c r="M11" t="n" s="0">
+        <v>14900.0</v>
+      </c>
+      <c r="N11" t="n" s="0">
+        <v>16000.0</v>
+      </c>
+      <c r="O11" t="n" s="0">
+        <v>16000.0</v>
+      </c>
+      <c r="P11" t="n" s="0">
+        <v>15200.0</v>
+      </c>
+      <c r="Q11" t="n" s="0">
+        <v>10500.0</v>
+      </c>
+      <c r="R11" t="n" s="0">
+        <v>18700.0</v>
+      </c>
+      <c r="S11" t="n" s="0">
+        <v>35500.0</v>
+      </c>
+      <c r="T11" t="n" s="0">
+        <v>19600.0</v>
+      </c>
+      <c r="U11" t="n" s="0">
+        <v>16700.0</v>
+      </c>
+      <c r="V11" t="n" s="0">
+        <v>17700.0</v>
+      </c>
+      <c r="W11" t="n" s="0">
+        <v>15200.0</v>
+      </c>
+      <c r="X11" t="n" s="0">
+        <v>16700.0</v>
+      </c>
+      <c r="Y11" t="n" s="0">
+        <v>15100.0</v>
+      </c>
+      <c r="Z11" t="n" s="0">
+        <v>26000.0</v>
+      </c>
+      <c r="AA11" t="n" s="0">
+        <v>17400.0</v>
+      </c>
+      <c r="AB11" t="n" s="0">
+        <v>25800.0</v>
+      </c>
+      <c r="AC11" t="n" s="0">
+        <v>23200.0</v>
+      </c>
+      <c r="AD11" t="n" s="0">
+        <v>15500.0</v>
+      </c>
+      <c r="AE11" t="n" s="0">
+        <v>13900.0</v>
+      </c>
+      <c r="AF11" t="n" s="0">
+        <v>16400.0</v>
+      </c>
+      <c r="AG11" t="n" s="0">
+        <v>16700.0</v>
+      </c>
+      <c r="AH11" t="n" s="0">
+        <v>10600.0</v>
+      </c>
+      <c r="AI11" t="n" s="0">
+        <v>16000.0</v>
+      </c>
+      <c r="AJ11" t="n" s="0">
+        <v>17200.0</v>
+      </c>
+      <c r="AK11" t="n" s="0">
+        <v>31700.0</v>
+      </c>
+      <c r="AL11" t="n" s="0">
+        <v>16700.0</v>
+      </c>
+      <c r="AM11" t="n" s="0">
+        <v>19500.0</v>
+      </c>
+      <c r="AN11" t="n" s="0">
+        <v>182400.0</v>
+      </c>
+      <c r="AO11" t="n" s="0">
+        <v>15000.0</v>
+      </c>
+      <c r="AP11" t="n" s="0">
+        <v>13100.0</v>
+      </c>
+      <c r="AQ11" t="n" s="0">
+        <v>14900.0</v>
+      </c>
+      <c r="AR11" t="n" s="0">
+        <v>16300.0</v>
+      </c>
+      <c r="AS11" t="n" s="0">
         <v>18100.0</v>
-      </c>
-      <c r="M11" t="n" s="0">
-        <v>11000.0</v>
-      </c>
-      <c r="N11" t="n" s="0">
-        <v>10200.0</v>
-      </c>
-      <c r="O11" t="n" s="0">
-        <v>16300.0</v>
-      </c>
-      <c r="P11" t="n" s="0">
-        <v>10300.0</v>
-      </c>
-      <c r="Q11" t="n" s="0">
-        <v>14700.0</v>
-      </c>
-      <c r="R11" t="n" s="0">
-        <v>9900.0</v>
-      </c>
-      <c r="S11" t="n" s="0">
-        <v>28700.0</v>
-      </c>
-      <c r="T11" t="n" s="0">
-        <v>29000.0</v>
-      </c>
-      <c r="U11" t="n" s="0">
-        <v>14200.0</v>
-      </c>
-      <c r="V11" t="n" s="0">
-        <v>15300.0</v>
-      </c>
-      <c r="W11" t="n" s="0">
-        <v>17600.0</v>
-      </c>
-      <c r="X11" t="n" s="0">
-        <v>16400.0</v>
-      </c>
-      <c r="Y11" t="n" s="0">
-        <v>16400.0</v>
-      </c>
-      <c r="Z11" t="n" s="0">
-        <v>11700.0</v>
-      </c>
-      <c r="AA11" t="n" s="0">
-        <v>17500.0</v>
-      </c>
-      <c r="AB11" t="n" s="0">
-        <v>18600.0</v>
-      </c>
-      <c r="AC11" t="n" s="0">
-        <v>15800.0</v>
-      </c>
-      <c r="AD11" t="n" s="0">
-        <v>17300.0</v>
-      </c>
-      <c r="AE11" t="n" s="0">
-        <v>15900.0</v>
-      </c>
-      <c r="AF11" t="n" s="0">
-        <v>15100.0</v>
-      </c>
-      <c r="AG11" t="n" s="0">
-        <v>16600.0</v>
-      </c>
-      <c r="AH11" t="n" s="0">
-        <v>15200.0</v>
-      </c>
-      <c r="AI11" t="n" s="0">
-        <v>10500.0</v>
-      </c>
-      <c r="AJ11" t="n" s="0">
-        <v>25100.0</v>
-      </c>
-      <c r="AK11" t="n" s="0">
-        <v>17400.0</v>
-      </c>
-      <c r="AL11" t="n" s="0">
-        <v>16200.0</v>
-      </c>
-      <c r="AM11" t="n" s="0">
-        <v>17000.0</v>
-      </c>
-      <c r="AN11" t="n" s="0">
-        <v>13900.0</v>
-      </c>
-      <c r="AO11" t="n" s="0">
-        <v>15400.0</v>
-      </c>
-      <c r="AP11" t="n" s="0">
-        <v>16400.0</v>
-      </c>
-      <c r="AQ11" t="n" s="0">
-        <v>13600.0</v>
-      </c>
-      <c r="AR11" t="n" s="0">
-        <v>15300.0</v>
-      </c>
-      <c r="AS11" t="n" s="0">
-        <v>27600.0</v>
       </c>
       <c r="AT11" t="n" s="0">
         <v>14800.0</v>
       </c>
       <c r="AU11" t="n" s="0">
-        <v>10600.0</v>
+        <v>14700.0</v>
       </c>
       <c r="AV11" t="n" s="0">
-        <v>15800.0</v>
+        <v>17000.0</v>
       </c>
       <c r="AW11" t="n" s="0">
-        <v>16300.0</v>
+        <v>68000.0</v>
       </c>
       <c r="AX11" t="n" s="0">
-        <v>17000.0</v>
+        <v>16000.0</v>
       </c>
       <c r="AY11" t="n" s="0">
-        <v>14700.0</v>
+        <v>26000.0</v>
       </c>
       <c r="AZ11" t="n" s="0">
-        <v>12600.0</v>
+        <v>14300.0</v>
       </c>
     </row>
   </sheetData>

--- a/excel/100(n)/RAW_Dataset.xlsx
+++ b/excel/100(n)/RAW_Dataset.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
   <si>
     <t xml:space="preserve">Algorithm </t>
   </si>
@@ -211,6 +211,156 @@
   </si>
   <si>
     <t>Trial 50</t>
+  </si>
+  <si>
+    <t>Trial 51</t>
+  </si>
+  <si>
+    <t>Trial 52</t>
+  </si>
+  <si>
+    <t>Trial 53</t>
+  </si>
+  <si>
+    <t>Trial 54</t>
+  </si>
+  <si>
+    <t>Trial 55</t>
+  </si>
+  <si>
+    <t>Trial 56</t>
+  </si>
+  <si>
+    <t>Trial 57</t>
+  </si>
+  <si>
+    <t>Trial 58</t>
+  </si>
+  <si>
+    <t>Trial 59</t>
+  </si>
+  <si>
+    <t>Trial 60</t>
+  </si>
+  <si>
+    <t>Trial 61</t>
+  </si>
+  <si>
+    <t>Trial 62</t>
+  </si>
+  <si>
+    <t>Trial 63</t>
+  </si>
+  <si>
+    <t>Trial 64</t>
+  </si>
+  <si>
+    <t>Trial 65</t>
+  </si>
+  <si>
+    <t>Trial 66</t>
+  </si>
+  <si>
+    <t>Trial 67</t>
+  </si>
+  <si>
+    <t>Trial 68</t>
+  </si>
+  <si>
+    <t>Trial 69</t>
+  </si>
+  <si>
+    <t>Trial 70</t>
+  </si>
+  <si>
+    <t>Trial 71</t>
+  </si>
+  <si>
+    <t>Trial 72</t>
+  </si>
+  <si>
+    <t>Trial 73</t>
+  </si>
+  <si>
+    <t>Trial 74</t>
+  </si>
+  <si>
+    <t>Trial 75</t>
+  </si>
+  <si>
+    <t>Trial 76</t>
+  </si>
+  <si>
+    <t>Trial 77</t>
+  </si>
+  <si>
+    <t>Trial 78</t>
+  </si>
+  <si>
+    <t>Trial 79</t>
+  </si>
+  <si>
+    <t>Trial 80</t>
+  </si>
+  <si>
+    <t>Trial 81</t>
+  </si>
+  <si>
+    <t>Trial 82</t>
+  </si>
+  <si>
+    <t>Trial 83</t>
+  </si>
+  <si>
+    <t>Trial 84</t>
+  </si>
+  <si>
+    <t>Trial 85</t>
+  </si>
+  <si>
+    <t>Trial 86</t>
+  </si>
+  <si>
+    <t>Trial 87</t>
+  </si>
+  <si>
+    <t>Trial 88</t>
+  </si>
+  <si>
+    <t>Trial 89</t>
+  </si>
+  <si>
+    <t>Trial 90</t>
+  </si>
+  <si>
+    <t>Trial 91</t>
+  </si>
+  <si>
+    <t>Trial 92</t>
+  </si>
+  <si>
+    <t>Trial 93</t>
+  </si>
+  <si>
+    <t>Trial 94</t>
+  </si>
+  <si>
+    <t>Trial 95</t>
+  </si>
+  <si>
+    <t>Trial 96</t>
+  </si>
+  <si>
+    <t>Trial 97</t>
+  </si>
+  <si>
+    <t>Trial 98</t>
+  </si>
+  <si>
+    <t>Trial 99</t>
+  </si>
+  <si>
+    <t>Trial 100</t>
   </si>
 </sst>
 </file>
@@ -542,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:CX11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="14.77734375"/>
@@ -706,6 +856,156 @@
       <c r="AZ1" t="s" s="0">
         <v>61</v>
       </c>
+      <c r="BA1" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="BB1" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="BC1" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="BD1" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="BE1" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="BF1" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="BG1" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="BH1" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="BI1" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="BJ1" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="BK1" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="BL1" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="BM1" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="BN1" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="BO1" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="BP1" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="BQ1" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="BR1" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="BS1" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BT1" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="BU1" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="BV1" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="BW1" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="BX1" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="BY1" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="BZ1" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="CA1" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="CB1" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="CC1" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="CD1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="CE1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="CF1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="CG1" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="CH1" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="CI1" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="CJ1" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="CK1" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="CL1" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="CM1" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="CN1" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="CO1" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="CP1" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="CQ1" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="CR1" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="CS1" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="CT1" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="CU1" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="CV1" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="CW1" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="CX1" t="s" s="0">
+        <v>111</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
@@ -715,154 +1015,304 @@
         <v>100.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>110600.0</v>
+        <v>113800.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>113600.0</v>
+        <v>113000.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>112700.0</v>
+        <v>113500.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>177500.0</v>
+        <v>166500.0</v>
       </c>
       <c r="G2" t="n" s="0">
-        <v>138800.0</v>
+        <v>178200.0</v>
       </c>
       <c r="H2" t="n" s="0">
-        <v>134400.0</v>
+        <v>136100.0</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>143600.0</v>
+        <v>171300.0</v>
       </c>
       <c r="J2" t="n" s="0">
-        <v>178000.0</v>
+        <v>182000.0</v>
       </c>
       <c r="K2" t="n" s="0">
-        <v>185700.0</v>
+        <v>183600.0</v>
       </c>
       <c r="L2" t="n" s="0">
-        <v>144300.0</v>
+        <v>112500.0</v>
       </c>
       <c r="M2" t="n" s="0">
-        <v>151300.0</v>
+        <v>115200.0</v>
       </c>
       <c r="N2" t="n" s="0">
-        <v>206800.0</v>
+        <v>127900.0</v>
       </c>
       <c r="O2" t="n" s="0">
-        <v>100300.0</v>
+        <v>84900.0</v>
       </c>
       <c r="P2" t="n" s="0">
-        <v>28600.0</v>
+        <v>20000.0</v>
       </c>
       <c r="Q2" t="n" s="0">
+        <v>17200.0</v>
+      </c>
+      <c r="R2" t="n" s="0">
+        <v>22400.0</v>
+      </c>
+      <c r="S2" t="n" s="0">
+        <v>36400.0</v>
+      </c>
+      <c r="T2" t="n" s="0">
+        <v>17700.0</v>
+      </c>
+      <c r="U2" t="n" s="0">
+        <v>34700.0</v>
+      </c>
+      <c r="V2" t="n" s="0">
+        <v>27100.0</v>
+      </c>
+      <c r="W2" t="n" s="0">
+        <v>31000.0</v>
+      </c>
+      <c r="X2" t="n" s="0">
+        <v>76900.0</v>
+      </c>
+      <c r="Y2" t="n" s="0">
+        <v>28100.0</v>
+      </c>
+      <c r="Z2" t="n" s="0">
+        <v>99400.0</v>
+      </c>
+      <c r="AA2" t="n" s="0">
+        <v>32700.0</v>
+      </c>
+      <c r="AB2" t="n" s="0">
+        <v>93100.0</v>
+      </c>
+      <c r="AC2" t="n" s="0">
+        <v>32500.0</v>
+      </c>
+      <c r="AD2" t="n" s="0">
+        <v>15500.0</v>
+      </c>
+      <c r="AE2" t="n" s="0">
+        <v>16100.0</v>
+      </c>
+      <c r="AF2" t="n" s="0">
+        <v>18800.0</v>
+      </c>
+      <c r="AG2" t="n" s="0">
+        <v>17900.0</v>
+      </c>
+      <c r="AH2" t="n" s="0">
+        <v>15700.0</v>
+      </c>
+      <c r="AI2" t="n" s="0">
         <v>15800.0</v>
       </c>
-      <c r="R2" t="n" s="0">
-        <v>31000.0</v>
-      </c>
-      <c r="S2" t="n" s="0">
-        <v>20000.0</v>
-      </c>
-      <c r="T2" t="n" s="0">
-        <v>18300.0</v>
-      </c>
-      <c r="U2" t="n" s="0">
-        <v>32900.0</v>
-      </c>
-      <c r="V2" t="n" s="0">
-        <v>32800.0</v>
-      </c>
-      <c r="W2" t="n" s="0">
-        <v>30400.0</v>
-      </c>
-      <c r="X2" t="n" s="0">
-        <v>33100.0</v>
-      </c>
-      <c r="Y2" t="n" s="0">
-        <v>29300.0</v>
-      </c>
-      <c r="Z2" t="n" s="0">
-        <v>50400.0</v>
-      </c>
-      <c r="AA2" t="n" s="0">
-        <v>87400.0</v>
-      </c>
-      <c r="AB2" t="n" s="0">
-        <v>31400.0</v>
-      </c>
-      <c r="AC2" t="n" s="0">
-        <v>28100.0</v>
-      </c>
-      <c r="AD2" t="n" s="0">
-        <v>18200.0</v>
-      </c>
-      <c r="AE2" t="n" s="0">
+      <c r="AJ2" t="n" s="0">
+        <v>15100.0</v>
+      </c>
+      <c r="AK2" t="n" s="0">
+        <v>15900.0</v>
+      </c>
+      <c r="AL2" t="n" s="0">
+        <v>15700.0</v>
+      </c>
+      <c r="AM2" t="n" s="0">
+        <v>15200.0</v>
+      </c>
+      <c r="AN2" t="n" s="0">
+        <v>14500.0</v>
+      </c>
+      <c r="AO2" t="n" s="0">
+        <v>19500.0</v>
+      </c>
+      <c r="AP2" t="n" s="0">
+        <v>18600.0</v>
+      </c>
+      <c r="AQ2" t="n" s="0">
+        <v>13000.0</v>
+      </c>
+      <c r="AR2" t="n" s="0">
+        <v>13300.0</v>
+      </c>
+      <c r="AS2" t="n" s="0">
+        <v>16600.0</v>
+      </c>
+      <c r="AT2" t="n" s="0">
+        <v>13700.0</v>
+      </c>
+      <c r="AU2" t="n" s="0">
+        <v>14700.0</v>
+      </c>
+      <c r="AV2" t="n" s="0">
+        <v>18500.0</v>
+      </c>
+      <c r="AW2" t="n" s="0">
+        <v>18400.0</v>
+      </c>
+      <c r="AX2" t="n" s="0">
+        <v>15900.0</v>
+      </c>
+      <c r="AY2" t="n" s="0">
+        <v>18700.0</v>
+      </c>
+      <c r="AZ2" t="n" s="0">
+        <v>15500.0</v>
+      </c>
+      <c r="BA2" t="n" s="0">
+        <v>24100.0</v>
+      </c>
+      <c r="BB2" t="n" s="0">
+        <v>16600.0</v>
+      </c>
+      <c r="BC2" t="n" s="0">
+        <v>15900.0</v>
+      </c>
+      <c r="BD2" t="n" s="0">
+        <v>16500.0</v>
+      </c>
+      <c r="BE2" t="n" s="0">
+        <v>13800.0</v>
+      </c>
+      <c r="BF2" t="n" s="0">
+        <v>17800.0</v>
+      </c>
+      <c r="BG2" t="n" s="0">
+        <v>12700.0</v>
+      </c>
+      <c r="BH2" t="n" s="0">
+        <v>12800.0</v>
+      </c>
+      <c r="BI2" t="n" s="0">
+        <v>12500.0</v>
+      </c>
+      <c r="BJ2" t="n" s="0">
+        <v>12100.0</v>
+      </c>
+      <c r="BK2" t="n" s="0">
+        <v>13200.0</v>
+      </c>
+      <c r="BL2" t="n" s="0">
+        <v>15800.0</v>
+      </c>
+      <c r="BM2" t="n" s="0">
+        <v>16900.0</v>
+      </c>
+      <c r="BN2" t="n" s="0">
+        <v>15900.0</v>
+      </c>
+      <c r="BO2" t="n" s="0">
+        <v>15500.0</v>
+      </c>
+      <c r="BP2" t="n" s="0">
+        <v>16500.0</v>
+      </c>
+      <c r="BQ2" t="n" s="0">
+        <v>14200.0</v>
+      </c>
+      <c r="BR2" t="n" s="0">
+        <v>18500.0</v>
+      </c>
+      <c r="BS2" t="n" s="0">
+        <v>17400.0</v>
+      </c>
+      <c r="BT2" t="n" s="0">
+        <v>15700.0</v>
+      </c>
+      <c r="BU2" t="n" s="0">
+        <v>16000.0</v>
+      </c>
+      <c r="BV2" t="n" s="0">
+        <v>13700.0</v>
+      </c>
+      <c r="BW2" t="n" s="0">
+        <v>13800.0</v>
+      </c>
+      <c r="BX2" t="n" s="0">
+        <v>13700.0</v>
+      </c>
+      <c r="BY2" t="n" s="0">
+        <v>14400.0</v>
+      </c>
+      <c r="BZ2" t="n" s="0">
+        <v>17200.0</v>
+      </c>
+      <c r="CA2" t="n" s="0">
+        <v>13200.0</v>
+      </c>
+      <c r="CB2" t="n" s="0">
+        <v>12900.0</v>
+      </c>
+      <c r="CC2" t="n" s="0">
+        <v>11400.0</v>
+      </c>
+      <c r="CD2" t="n" s="0">
         <v>16700.0</v>
       </c>
-      <c r="AF2" t="n" s="0">
-        <v>18500.0</v>
-      </c>
-      <c r="AG2" t="n" s="0">
-        <v>19600.0</v>
-      </c>
-      <c r="AH2" t="n" s="0">
-        <v>15500.0</v>
-      </c>
-      <c r="AI2" t="n" s="0">
-        <v>16700.0</v>
-      </c>
-      <c r="AJ2" t="n" s="0">
-        <v>24000.0</v>
-      </c>
-      <c r="AK2" t="n" s="0">
-        <v>18100.0</v>
-      </c>
-      <c r="AL2" t="n" s="0">
+      <c r="CE2" t="n" s="0">
+        <v>15900.0</v>
+      </c>
+      <c r="CF2" t="n" s="0">
+        <v>15900.0</v>
+      </c>
+      <c r="CG2" t="n" s="0">
+        <v>16100.0</v>
+      </c>
+      <c r="CH2" t="n" s="0">
+        <v>12100.0</v>
+      </c>
+      <c r="CI2" t="n" s="0">
+        <v>14300.0</v>
+      </c>
+      <c r="CJ2" t="n" s="0">
+        <v>13000.0</v>
+      </c>
+      <c r="CK2" t="n" s="0">
+        <v>13200.0</v>
+      </c>
+      <c r="CL2" t="n" s="0">
+        <v>15900.0</v>
+      </c>
+      <c r="CM2" t="n" s="0">
+        <v>16000.0</v>
+      </c>
+      <c r="CN2" t="n" s="0">
+        <v>16200.0</v>
+      </c>
+      <c r="CO2" t="n" s="0">
+        <v>14500.0</v>
+      </c>
+      <c r="CP2" t="n" s="0">
+        <v>14400.0</v>
+      </c>
+      <c r="CQ2" t="n" s="0">
         <v>14600.0</v>
       </c>
-      <c r="AM2" t="n" s="0">
+      <c r="CR2" t="n" s="0">
+        <v>17000.0</v>
+      </c>
+      <c r="CS2" t="n" s="0">
         <v>17200.0</v>
       </c>
-      <c r="AN2" t="n" s="0">
-        <v>20900.0</v>
-      </c>
-      <c r="AO2" t="n" s="0">
-        <v>16600.0</v>
-      </c>
-      <c r="AP2" t="n" s="0">
-        <v>17300.0</v>
-      </c>
-      <c r="AQ2" t="n" s="0">
-        <v>17800.0</v>
-      </c>
-      <c r="AR2" t="n" s="0">
-        <v>18400.0</v>
-      </c>
-      <c r="AS2" t="n" s="0">
-        <v>16900.0</v>
-      </c>
-      <c r="AT2" t="n" s="0">
-        <v>17100.0</v>
-      </c>
-      <c r="AU2" t="n" s="0">
-        <v>16800.0</v>
-      </c>
-      <c r="AV2" t="n" s="0">
-        <v>16500.0</v>
-      </c>
-      <c r="AW2" t="n" s="0">
-        <v>17600.0</v>
-      </c>
-      <c r="AX2" t="n" s="0">
-        <v>17500.0</v>
-      </c>
-      <c r="AY2" t="n" s="0">
-        <v>18200.0</v>
-      </c>
-      <c r="AZ2" t="n" s="0">
-        <v>16700.0</v>
+      <c r="CT2" t="n" s="0">
+        <v>13600.0</v>
+      </c>
+      <c r="CU2" t="n" s="0">
+        <v>13600.0</v>
+      </c>
+      <c r="CV2" t="n" s="0">
+        <v>13500.0</v>
+      </c>
+      <c r="CW2" t="n" s="0">
+        <v>12700.0</v>
+      </c>
+      <c r="CX2" t="n" s="0">
+        <v>16300.0</v>
       </c>
     </row>
     <row r="3">
@@ -873,154 +1323,304 @@
         <v>100.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>112700.0</v>
+        <v>114100.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>112600.0</v>
+        <v>112300.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>112700.0</v>
+        <v>112500.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>172900.0</v>
+        <v>160400.0</v>
       </c>
       <c r="G3" t="n" s="0">
-        <v>140500.0</v>
+        <v>214400.0</v>
       </c>
       <c r="H3" t="n" s="0">
-        <v>137900.0</v>
+        <v>138400.0</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>149300.0</v>
+        <v>112300.0</v>
       </c>
       <c r="J3" t="n" s="0">
-        <v>180900.0</v>
+        <v>171600.0</v>
       </c>
       <c r="K3" t="n" s="0">
-        <v>173300.0</v>
+        <v>181700.0</v>
       </c>
       <c r="L3" t="n" s="0">
-        <v>121800.0</v>
+        <v>187200.0</v>
       </c>
       <c r="M3" t="n" s="0">
-        <v>142700.0</v>
+        <v>111400.0</v>
       </c>
       <c r="N3" t="n" s="0">
-        <v>196800.0</v>
+        <v>124400.0</v>
       </c>
       <c r="O3" t="n" s="0">
-        <v>73200.0</v>
+        <v>88300.0</v>
       </c>
       <c r="P3" t="n" s="0">
-        <v>30200.0</v>
+        <v>19200.0</v>
       </c>
       <c r="Q3" t="n" s="0">
+        <v>16200.0</v>
+      </c>
+      <c r="R3" t="n" s="0">
+        <v>17900.0</v>
+      </c>
+      <c r="S3" t="n" s="0">
+        <v>31800.0</v>
+      </c>
+      <c r="T3" t="n" s="0">
+        <v>30000.0</v>
+      </c>
+      <c r="U3" t="n" s="0">
+        <v>30300.0</v>
+      </c>
+      <c r="V3" t="n" s="0">
+        <v>32700.0</v>
+      </c>
+      <c r="W3" t="n" s="0">
+        <v>31400.0</v>
+      </c>
+      <c r="X3" t="n" s="0">
+        <v>48500.0</v>
+      </c>
+      <c r="Y3" t="n" s="0">
+        <v>28200.0</v>
+      </c>
+      <c r="Z3" t="n" s="0">
+        <v>74800.0</v>
+      </c>
+      <c r="AA3" t="n" s="0">
+        <v>43700.0</v>
+      </c>
+      <c r="AB3" t="n" s="0">
+        <v>101100.0</v>
+      </c>
+      <c r="AC3" t="n" s="0">
+        <v>37500.0</v>
+      </c>
+      <c r="AD3" t="n" s="0">
+        <v>24000.0</v>
+      </c>
+      <c r="AE3" t="n" s="0">
         <v>16800.0</v>
       </c>
-      <c r="R3" t="n" s="0">
-        <v>30700.0</v>
-      </c>
-      <c r="S3" t="n" s="0">
-        <v>18200.0</v>
-      </c>
-      <c r="T3" t="n" s="0">
-        <v>21400.0</v>
-      </c>
-      <c r="U3" t="n" s="0">
-        <v>31300.0</v>
-      </c>
-      <c r="V3" t="n" s="0">
-        <v>30700.0</v>
-      </c>
-      <c r="W3" t="n" s="0">
-        <v>30600.0</v>
-      </c>
-      <c r="X3" t="n" s="0">
-        <v>59000.0</v>
-      </c>
-      <c r="Y3" t="n" s="0">
-        <v>29900.0</v>
-      </c>
-      <c r="Z3" t="n" s="0">
-        <v>116800.0</v>
-      </c>
-      <c r="AA3" t="n" s="0">
-        <v>28900.0</v>
-      </c>
-      <c r="AB3" t="n" s="0">
-        <v>19800.0</v>
-      </c>
-      <c r="AC3" t="n" s="0">
-        <v>23100.0</v>
-      </c>
-      <c r="AD3" t="n" s="0">
+      <c r="AF3" t="n" s="0">
+        <v>16800.0</v>
+      </c>
+      <c r="AG3" t="n" s="0">
+        <v>15900.0</v>
+      </c>
+      <c r="AH3" t="n" s="0">
+        <v>17800.0</v>
+      </c>
+      <c r="AI3" t="n" s="0">
+        <v>17100.0</v>
+      </c>
+      <c r="AJ3" t="n" s="0">
+        <v>17300.0</v>
+      </c>
+      <c r="AK3" t="n" s="0">
+        <v>16700.0</v>
+      </c>
+      <c r="AL3" t="n" s="0">
+        <v>16000.0</v>
+      </c>
+      <c r="AM3" t="n" s="0">
+        <v>16700.0</v>
+      </c>
+      <c r="AN3" t="n" s="0">
+        <v>14200.0</v>
+      </c>
+      <c r="AO3" t="n" s="0">
+        <v>17200.0</v>
+      </c>
+      <c r="AP3" t="n" s="0">
+        <v>18700.0</v>
+      </c>
+      <c r="AQ3" t="n" s="0">
+        <v>14500.0</v>
+      </c>
+      <c r="AR3" t="n" s="0">
+        <v>12800.0</v>
+      </c>
+      <c r="AS3" t="n" s="0">
+        <v>18100.0</v>
+      </c>
+      <c r="AT3" t="n" s="0">
+        <v>14500.0</v>
+      </c>
+      <c r="AU3" t="n" s="0">
+        <v>13700.0</v>
+      </c>
+      <c r="AV3" t="n" s="0">
+        <v>16400.0</v>
+      </c>
+      <c r="AW3" t="n" s="0">
+        <v>15300.0</v>
+      </c>
+      <c r="AX3" t="n" s="0">
+        <v>15800.0</v>
+      </c>
+      <c r="AY3" t="n" s="0">
+        <v>17300.0</v>
+      </c>
+      <c r="AZ3" t="n" s="0">
+        <v>17800.0</v>
+      </c>
+      <c r="BA3" t="n" s="0">
+        <v>13000.0</v>
+      </c>
+      <c r="BB3" t="n" s="0">
+        <v>16400.0</v>
+      </c>
+      <c r="BC3" t="n" s="0">
+        <v>18100.0</v>
+      </c>
+      <c r="BD3" t="n" s="0">
+        <v>18500.0</v>
+      </c>
+      <c r="BE3" t="n" s="0">
+        <v>12500.0</v>
+      </c>
+      <c r="BF3" t="n" s="0">
+        <v>17900.0</v>
+      </c>
+      <c r="BG3" t="n" s="0">
+        <v>12800.0</v>
+      </c>
+      <c r="BH3" t="n" s="0">
+        <v>13600.0</v>
+      </c>
+      <c r="BI3" t="n" s="0">
+        <v>13800.0</v>
+      </c>
+      <c r="BJ3" t="n" s="0">
+        <v>13600.0</v>
+      </c>
+      <c r="BK3" t="n" s="0">
+        <v>12700.0</v>
+      </c>
+      <c r="BL3" t="n" s="0">
+        <v>17000.0</v>
+      </c>
+      <c r="BM3" t="n" s="0">
+        <v>18800.0</v>
+      </c>
+      <c r="BN3" t="n" s="0">
+        <v>17600.0</v>
+      </c>
+      <c r="BO3" t="n" s="0">
+        <v>17700.0</v>
+      </c>
+      <c r="BP3" t="n" s="0">
+        <v>17200.0</v>
+      </c>
+      <c r="BQ3" t="n" s="0">
+        <v>13200.0</v>
+      </c>
+      <c r="BR3" t="n" s="0">
+        <v>20500.0</v>
+      </c>
+      <c r="BS3" t="n" s="0">
+        <v>16400.0</v>
+      </c>
+      <c r="BT3" t="n" s="0">
+        <v>16800.0</v>
+      </c>
+      <c r="BU3" t="n" s="0">
+        <v>18800.0</v>
+      </c>
+      <c r="BV3" t="n" s="0">
+        <v>12200.0</v>
+      </c>
+      <c r="BW3" t="n" s="0">
+        <v>14300.0</v>
+      </c>
+      <c r="BX3" t="n" s="0">
+        <v>14900.0</v>
+      </c>
+      <c r="BY3" t="n" s="0">
+        <v>15000.0</v>
+      </c>
+      <c r="BZ3" t="n" s="0">
+        <v>16600.0</v>
+      </c>
+      <c r="CA3" t="n" s="0">
+        <v>12500.0</v>
+      </c>
+      <c r="CB3" t="n" s="0">
+        <v>13800.0</v>
+      </c>
+      <c r="CC3" t="n" s="0">
+        <v>12200.0</v>
+      </c>
+      <c r="CD3" t="n" s="0">
+        <v>16900.0</v>
+      </c>
+      <c r="CE3" t="n" s="0">
+        <v>16300.0</v>
+      </c>
+      <c r="CF3" t="n" s="0">
+        <v>17400.0</v>
+      </c>
+      <c r="CG3" t="n" s="0">
+        <v>16800.0</v>
+      </c>
+      <c r="CH3" t="n" s="0">
+        <v>14500.0</v>
+      </c>
+      <c r="CI3" t="n" s="0">
+        <v>14900.0</v>
+      </c>
+      <c r="CJ3" t="n" s="0">
+        <v>14600.0</v>
+      </c>
+      <c r="CK3" t="n" s="0">
+        <v>12600.0</v>
+      </c>
+      <c r="CL3" t="n" s="0">
+        <v>17400.0</v>
+      </c>
+      <c r="CM3" t="n" s="0">
+        <v>17100.0</v>
+      </c>
+      <c r="CN3" t="n" s="0">
+        <v>17900.0</v>
+      </c>
+      <c r="CO3" t="n" s="0">
         <v>13400.0</v>
       </c>
-      <c r="AE3" t="n" s="0">
-        <v>15700.0</v>
-      </c>
-      <c r="AF3" t="n" s="0">
-        <v>16400.0</v>
-      </c>
-      <c r="AG3" t="n" s="0">
-        <v>18000.0</v>
-      </c>
-      <c r="AH3" t="n" s="0">
-        <v>15500.0</v>
-      </c>
-      <c r="AI3" t="n" s="0">
-        <v>16400.0</v>
-      </c>
-      <c r="AJ3" t="n" s="0">
-        <v>30500.0</v>
-      </c>
-      <c r="AK3" t="n" s="0">
-        <v>15900.0</v>
-      </c>
-      <c r="AL3" t="n" s="0">
-        <v>17400.0</v>
-      </c>
-      <c r="AM3" t="n" s="0">
-        <v>20500.0</v>
-      </c>
-      <c r="AN3" t="n" s="0">
-        <v>14700.0</v>
-      </c>
-      <c r="AO3" t="n" s="0">
-        <v>18500.0</v>
-      </c>
-      <c r="AP3" t="n" s="0">
+      <c r="CP3" t="n" s="0">
+        <v>13900.0</v>
+      </c>
+      <c r="CQ3" t="n" s="0">
+        <v>18900.0</v>
+      </c>
+      <c r="CR3" t="n" s="0">
+        <v>16500.0</v>
+      </c>
+      <c r="CS3" t="n" s="0">
         <v>17600.0</v>
       </c>
-      <c r="AQ3" t="n" s="0">
-        <v>17300.0</v>
-      </c>
-      <c r="AR3" t="n" s="0">
-        <v>17600.0</v>
-      </c>
-      <c r="AS3" t="n" s="0">
-        <v>17700.0</v>
-      </c>
-      <c r="AT3" t="n" s="0">
-        <v>16400.0</v>
-      </c>
-      <c r="AU3" t="n" s="0">
-        <v>19300.0</v>
-      </c>
-      <c r="AV3" t="n" s="0">
-        <v>19400.0</v>
-      </c>
-      <c r="AW3" t="n" s="0">
-        <v>17900.0</v>
-      </c>
-      <c r="AX3" t="n" s="0">
-        <v>18500.0</v>
-      </c>
-      <c r="AY3" t="n" s="0">
-        <v>16400.0</v>
-      </c>
-      <c r="AZ3" t="n" s="0">
-        <v>17300.0</v>
+      <c r="CT3" t="n" s="0">
+        <v>13700.0</v>
+      </c>
+      <c r="CU3" t="n" s="0">
+        <v>13300.0</v>
+      </c>
+      <c r="CV3" t="n" s="0">
+        <v>13500.0</v>
+      </c>
+      <c r="CW3" t="n" s="0">
+        <v>13300.0</v>
+      </c>
+      <c r="CX3" t="n" s="0">
+        <v>17800.0</v>
       </c>
     </row>
     <row r="4">
@@ -1031,154 +1631,304 @@
         <v>100.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>115900.0</v>
+        <v>74300.0</v>
       </c>
       <c r="D4" t="n" s="0">
+        <v>40500.0</v>
+      </c>
+      <c r="E4" t="n" s="0">
+        <v>38100.0</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>53900.0</v>
+      </c>
+      <c r="G4" t="n" s="0">
+        <v>70700.0</v>
+      </c>
+      <c r="H4" t="n" s="0">
+        <v>44700.0</v>
+      </c>
+      <c r="I4" t="n" s="0">
+        <v>40100.0</v>
+      </c>
+      <c r="J4" t="n" s="0">
+        <v>60500.0</v>
+      </c>
+      <c r="K4" t="n" s="0">
+        <v>63800.0</v>
+      </c>
+      <c r="L4" t="n" s="0">
+        <v>60600.0</v>
+      </c>
+      <c r="M4" t="n" s="0">
+        <v>41600.0</v>
+      </c>
+      <c r="N4" t="n" s="0">
+        <v>37500.0</v>
+      </c>
+      <c r="O4" t="n" s="0">
+        <v>56600.0</v>
+      </c>
+      <c r="P4" t="n" s="0">
         <v>38000.0</v>
       </c>
-      <c r="E4" t="n" s="0">
-        <v>39000.0</v>
-      </c>
-      <c r="F4" t="n" s="0">
-        <v>61500.0</v>
-      </c>
-      <c r="G4" t="n" s="0">
-        <v>47400.0</v>
-      </c>
-      <c r="H4" t="n" s="0">
-        <v>40600.0</v>
-      </c>
-      <c r="I4" t="n" s="0">
-        <v>60300.0</v>
-      </c>
-      <c r="J4" t="n" s="0">
-        <v>58000.0</v>
-      </c>
-      <c r="K4" t="n" s="0">
-        <v>62800.0</v>
-      </c>
-      <c r="L4" t="n" s="0">
-        <v>39800.0</v>
-      </c>
-      <c r="M4" t="n" s="0">
-        <v>47900.0</v>
-      </c>
-      <c r="N4" t="n" s="0">
-        <v>69500.0</v>
-      </c>
-      <c r="O4" t="n" s="0">
-        <v>94700.0</v>
-      </c>
-      <c r="P4" t="n" s="0">
-        <v>60400.0</v>
-      </c>
       <c r="Q4" t="n" s="0">
-        <v>41900.0</v>
+        <v>42500.0</v>
       </c>
       <c r="R4" t="n" s="0">
-        <v>67200.0</v>
+        <v>39900.0</v>
       </c>
       <c r="S4" t="n" s="0">
-        <v>42400.0</v>
+        <v>60100.0</v>
       </c>
       <c r="T4" t="n" s="0">
-        <v>51800.0</v>
+        <v>70100.0</v>
       </c>
       <c r="U4" t="n" s="0">
-        <v>68500.0</v>
+        <v>53700.0</v>
       </c>
       <c r="V4" t="n" s="0">
-        <v>63000.0</v>
+        <v>58800.0</v>
       </c>
       <c r="W4" t="n" s="0">
-        <v>57600.0</v>
+        <v>61300.0</v>
       </c>
       <c r="X4" t="n" s="0">
-        <v>59300.0</v>
+        <v>49500.0</v>
       </c>
       <c r="Y4" t="n" s="0">
-        <v>53000.0</v>
+        <v>55400.0</v>
       </c>
       <c r="Z4" t="n" s="0">
-        <v>78000.0</v>
+        <v>54000.0</v>
       </c>
       <c r="AA4" t="n" s="0">
-        <v>50100.0</v>
+        <v>125400.0</v>
       </c>
       <c r="AB4" t="n" s="0">
+        <v>13300.0</v>
+      </c>
+      <c r="AC4" t="n" s="0">
+        <v>10500.0</v>
+      </c>
+      <c r="AD4" t="n" s="0">
+        <v>16400.0</v>
+      </c>
+      <c r="AE4" t="n" s="0">
+        <v>10300.0</v>
+      </c>
+      <c r="AF4" t="n" s="0">
         <v>12800.0</v>
-      </c>
-      <c r="AC4" t="n" s="0">
-        <v>17400.0</v>
-      </c>
-      <c r="AD4" t="n" s="0">
-        <v>7300.0</v>
-      </c>
-      <c r="AE4" t="n" s="0">
-        <v>9300.0</v>
-      </c>
-      <c r="AF4" t="n" s="0">
-        <v>11200.0</v>
       </c>
       <c r="AG4" t="n" s="0">
         <v>14200.0</v>
       </c>
       <c r="AH4" t="n" s="0">
-        <v>5900.0</v>
+        <v>10700.0</v>
       </c>
       <c r="AI4" t="n" s="0">
-        <v>10900.0</v>
+        <v>10100.0</v>
       </c>
       <c r="AJ4" t="n" s="0">
-        <v>14300.0</v>
+        <v>13500.0</v>
       </c>
       <c r="AK4" t="n" s="0">
-        <v>8500.0</v>
+        <v>7600.0</v>
       </c>
       <c r="AL4" t="n" s="0">
-        <v>7000.0</v>
+        <v>7100.0</v>
       </c>
       <c r="AM4" t="n" s="0">
-        <v>24500.0</v>
+        <v>11300.0</v>
       </c>
       <c r="AN4" t="n" s="0">
-        <v>6300.0</v>
+        <v>5600.0</v>
       </c>
       <c r="AO4" t="n" s="0">
+        <v>12200.0</v>
+      </c>
+      <c r="AP4" t="n" s="0">
         <v>10000.0</v>
       </c>
-      <c r="AP4" t="n" s="0">
-        <v>10100.0</v>
-      </c>
       <c r="AQ4" t="n" s="0">
-        <v>12800.0</v>
+        <v>37200.0</v>
       </c>
       <c r="AR4" t="n" s="0">
-        <v>9600.0</v>
+        <v>5500.0</v>
       </c>
       <c r="AS4" t="n" s="0">
-        <v>9700.0</v>
+        <v>10800.0</v>
       </c>
       <c r="AT4" t="n" s="0">
-        <v>26300.0</v>
+        <v>72000.0</v>
       </c>
       <c r="AU4" t="n" s="0">
-        <v>9200.0</v>
+        <v>5400.0</v>
       </c>
       <c r="AV4" t="n" s="0">
-        <v>9900.0</v>
+        <v>72900.0</v>
       </c>
       <c r="AW4" t="n" s="0">
-        <v>63000.0</v>
+        <v>54400.0</v>
       </c>
       <c r="AX4" t="n" s="0">
-        <v>86900.0</v>
+        <v>4200.0</v>
       </c>
       <c r="AY4" t="n" s="0">
-        <v>41200.0</v>
+        <v>2600.0</v>
       </c>
       <c r="AZ4" t="n" s="0">
-        <v>5600.0</v>
+        <v>2700.0</v>
+      </c>
+      <c r="BA4" t="n" s="0">
+        <v>2400.0</v>
+      </c>
+      <c r="BB4" t="n" s="0">
+        <v>2600.0</v>
+      </c>
+      <c r="BC4" t="n" s="0">
+        <v>2500.0</v>
+      </c>
+      <c r="BD4" t="n" s="0">
+        <v>2500.0</v>
+      </c>
+      <c r="BE4" t="n" s="0">
+        <v>2200.0</v>
+      </c>
+      <c r="BF4" t="n" s="0">
+        <v>2600.0</v>
+      </c>
+      <c r="BG4" t="n" s="0">
+        <v>2400.0</v>
+      </c>
+      <c r="BH4" t="n" s="0">
+        <v>2300.0</v>
+      </c>
+      <c r="BI4" t="n" s="0">
+        <v>2800.0</v>
+      </c>
+      <c r="BJ4" t="n" s="0">
+        <v>2200.0</v>
+      </c>
+      <c r="BK4" t="n" s="0">
+        <v>2300.0</v>
+      </c>
+      <c r="BL4" t="n" s="0">
+        <v>2600.0</v>
+      </c>
+      <c r="BM4" t="n" s="0">
+        <v>2500.0</v>
+      </c>
+      <c r="BN4" t="n" s="0">
+        <v>4100.0</v>
+      </c>
+      <c r="BO4" t="n" s="0">
+        <v>2500.0</v>
+      </c>
+      <c r="BP4" t="n" s="0">
+        <v>3000.0</v>
+      </c>
+      <c r="BQ4" t="n" s="0">
+        <v>2800.0</v>
+      </c>
+      <c r="BR4" t="n" s="0">
+        <v>2600.0</v>
+      </c>
+      <c r="BS4" t="n" s="0">
+        <v>2500.0</v>
+      </c>
+      <c r="BT4" t="n" s="0">
+        <v>2700.0</v>
+      </c>
+      <c r="BU4" t="n" s="0">
+        <v>2800.0</v>
+      </c>
+      <c r="BV4" t="n" s="0">
+        <v>2500.0</v>
+      </c>
+      <c r="BW4" t="n" s="0">
+        <v>2500.0</v>
+      </c>
+      <c r="BX4" t="n" s="0">
+        <v>1900.0</v>
+      </c>
+      <c r="BY4" t="n" s="0">
+        <v>2100.0</v>
+      </c>
+      <c r="BZ4" t="n" s="0">
+        <v>2600.0</v>
+      </c>
+      <c r="CA4" t="n" s="0">
+        <v>2200.0</v>
+      </c>
+      <c r="CB4" t="n" s="0">
+        <v>2400.0</v>
+      </c>
+      <c r="CC4" t="n" s="0">
+        <v>2300.0</v>
+      </c>
+      <c r="CD4" t="n" s="0">
+        <v>2400.0</v>
+      </c>
+      <c r="CE4" t="n" s="0">
+        <v>2400.0</v>
+      </c>
+      <c r="CF4" t="n" s="0">
+        <v>2400.0</v>
+      </c>
+      <c r="CG4" t="n" s="0">
+        <v>2600.0</v>
+      </c>
+      <c r="CH4" t="n" s="0">
+        <v>2700.0</v>
+      </c>
+      <c r="CI4" t="n" s="0">
+        <v>2100.0</v>
+      </c>
+      <c r="CJ4" t="n" s="0">
+        <v>2100.0</v>
+      </c>
+      <c r="CK4" t="n" s="0">
+        <v>2200.0</v>
+      </c>
+      <c r="CL4" t="n" s="0">
+        <v>2500.0</v>
+      </c>
+      <c r="CM4" t="n" s="0">
+        <v>2600.0</v>
+      </c>
+      <c r="CN4" t="n" s="0">
+        <v>2900.0</v>
+      </c>
+      <c r="CO4" t="n" s="0">
+        <v>2200.0</v>
+      </c>
+      <c r="CP4" t="n" s="0">
+        <v>2800.0</v>
+      </c>
+      <c r="CQ4" t="n" s="0">
+        <v>2100.0</v>
+      </c>
+      <c r="CR4" t="n" s="0">
+        <v>3100.0</v>
+      </c>
+      <c r="CS4" t="n" s="0">
+        <v>2500.0</v>
+      </c>
+      <c r="CT4" t="n" s="0">
+        <v>2300.0</v>
+      </c>
+      <c r="CU4" t="n" s="0">
+        <v>2300.0</v>
+      </c>
+      <c r="CV4" t="n" s="0">
+        <v>2000.0</v>
+      </c>
+      <c r="CW4" t="n" s="0">
+        <v>2500.0</v>
+      </c>
+      <c r="CX4" t="n" s="0">
+        <v>2600.0</v>
       </c>
     </row>
     <row r="5">
@@ -1189,154 +1939,304 @@
         <v>100.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>40600.0</v>
+        <v>42700.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>39200.0</v>
+        <v>50100.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>48000.0</v>
+        <v>41600.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>57800.0</v>
+        <v>54300.0</v>
       </c>
       <c r="G5" t="n" s="0">
-        <v>49400.0</v>
+        <v>54300.0</v>
       </c>
       <c r="H5" t="n" s="0">
-        <v>49800.0</v>
+        <v>48500.0</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>46300.0</v>
+        <v>36600.0</v>
       </c>
       <c r="J5" t="n" s="0">
-        <v>67300.0</v>
+        <v>57900.0</v>
       </c>
       <c r="K5" t="n" s="0">
-        <v>56100.0</v>
+        <v>63700.0</v>
       </c>
       <c r="L5" t="n" s="0">
-        <v>41300.0</v>
+        <v>70000.0</v>
       </c>
       <c r="M5" t="n" s="0">
-        <v>48000.0</v>
+        <v>36000.0</v>
       </c>
       <c r="N5" t="n" s="0">
-        <v>62300.0</v>
+        <v>39100.0</v>
       </c>
       <c r="O5" t="n" s="0">
-        <v>54800.0</v>
+        <v>66000.0</v>
       </c>
       <c r="P5" t="n" s="0">
-        <v>41400.0</v>
+        <v>40000.0</v>
       </c>
       <c r="Q5" t="n" s="0">
-        <v>37700.0</v>
+        <v>36600.0</v>
       </c>
       <c r="R5" t="n" s="0">
-        <v>57100.0</v>
+        <v>37400.0</v>
       </c>
       <c r="S5" t="n" s="0">
-        <v>35500.0</v>
+        <v>58700.0</v>
       </c>
       <c r="T5" t="n" s="0">
-        <v>37300.0</v>
+        <v>57700.0</v>
       </c>
       <c r="U5" t="n" s="0">
-        <v>55600.0</v>
+        <v>67200.0</v>
       </c>
       <c r="V5" t="n" s="0">
-        <v>59200.0</v>
+        <v>46700.0</v>
       </c>
       <c r="W5" t="n" s="0">
-        <v>46500.0</v>
+        <v>62000.0</v>
       </c>
       <c r="X5" t="n" s="0">
-        <v>64200.0</v>
+        <v>58900.0</v>
       </c>
       <c r="Y5" t="n" s="0">
-        <v>54500.0</v>
+        <v>40000.0</v>
       </c>
       <c r="Z5" t="n" s="0">
-        <v>62100.0</v>
+        <v>47100.0</v>
       </c>
       <c r="AA5" t="n" s="0">
-        <v>73800.0</v>
+        <v>68600.0</v>
       </c>
       <c r="AB5" t="n" s="0">
-        <v>47500.0</v>
+        <v>11500.0</v>
       </c>
       <c r="AC5" t="n" s="0">
-        <v>11800.0</v>
+        <v>10800.0</v>
       </c>
       <c r="AD5" t="n" s="0">
-        <v>5800.0</v>
+        <v>14400.0</v>
       </c>
       <c r="AE5" t="n" s="0">
-        <v>8900.0</v>
+        <v>10900.0</v>
       </c>
       <c r="AF5" t="n" s="0">
+        <v>9600.0</v>
+      </c>
+      <c r="AG5" t="n" s="0">
+        <v>10900.0</v>
+      </c>
+      <c r="AH5" t="n" s="0">
+        <v>11000.0</v>
+      </c>
+      <c r="AI5" t="n" s="0">
+        <v>9700.0</v>
+      </c>
+      <c r="AJ5" t="n" s="0">
+        <v>9200.0</v>
+      </c>
+      <c r="AK5" t="n" s="0">
+        <v>8200.0</v>
+      </c>
+      <c r="AL5" t="n" s="0">
+        <v>7000.0</v>
+      </c>
+      <c r="AM5" t="n" s="0">
+        <v>8500.0</v>
+      </c>
+      <c r="AN5" t="n" s="0">
+        <v>5500.0</v>
+      </c>
+      <c r="AO5" t="n" s="0">
+        <v>9800.0</v>
+      </c>
+      <c r="AP5" t="n" s="0">
+        <v>47900.0</v>
+      </c>
+      <c r="AQ5" t="n" s="0">
+        <v>6000.0</v>
+      </c>
+      <c r="AR5" t="n" s="0">
+        <v>5400.0</v>
+      </c>
+      <c r="AS5" t="n" s="0">
         <v>10100.0</v>
       </c>
-      <c r="AG5" t="n" s="0">
-        <v>10500.0</v>
-      </c>
-      <c r="AH5" t="n" s="0">
-        <v>10600.0</v>
-      </c>
-      <c r="AI5" t="n" s="0">
-        <v>10100.0</v>
-      </c>
-      <c r="AJ5" t="n" s="0">
-        <v>12800.0</v>
-      </c>
-      <c r="AK5" t="n" s="0">
-        <v>12400.0</v>
-      </c>
-      <c r="AL5" t="n" s="0">
-        <v>7100.0</v>
-      </c>
-      <c r="AM5" t="n" s="0">
-        <v>9300.0</v>
-      </c>
-      <c r="AN5" t="n" s="0">
-        <v>7700.0</v>
-      </c>
-      <c r="AO5" t="n" s="0">
-        <v>11300.0</v>
-      </c>
-      <c r="AP5" t="n" s="0">
-        <v>8700.0</v>
-      </c>
-      <c r="AQ5" t="n" s="0">
-        <v>11000.0</v>
-      </c>
-      <c r="AR5" t="n" s="0">
-        <v>11300.0</v>
-      </c>
-      <c r="AS5" t="n" s="0">
-        <v>11600.0</v>
-      </c>
       <c r="AT5" t="n" s="0">
-        <v>17000.0</v>
+        <v>37400.0</v>
       </c>
       <c r="AU5" t="n" s="0">
-        <v>9400.0</v>
+        <v>5300.0</v>
       </c>
       <c r="AV5" t="n" s="0">
-        <v>11700.0</v>
+        <v>51400.0</v>
       </c>
       <c r="AW5" t="n" s="0">
-        <v>63000.0</v>
+        <v>32200.0</v>
       </c>
       <c r="AX5" t="n" s="0">
-        <v>61400.0</v>
+        <v>3500.0</v>
       </c>
       <c r="AY5" t="n" s="0">
-        <v>30300.0</v>
+        <v>2700.0</v>
       </c>
       <c r="AZ5" t="n" s="0">
-        <v>3500.0</v>
+        <v>2400.0</v>
+      </c>
+      <c r="BA5" t="n" s="0">
+        <v>2100.0</v>
+      </c>
+      <c r="BB5" t="n" s="0">
+        <v>2300.0</v>
+      </c>
+      <c r="BC5" t="n" s="0">
+        <v>2500.0</v>
+      </c>
+      <c r="BD5" t="n" s="0">
+        <v>2400.0</v>
+      </c>
+      <c r="BE5" t="n" s="0">
+        <v>1900.0</v>
+      </c>
+      <c r="BF5" t="n" s="0">
+        <v>2400.0</v>
+      </c>
+      <c r="BG5" t="n" s="0">
+        <v>2000.0</v>
+      </c>
+      <c r="BH5" t="n" s="0">
+        <v>1900.0</v>
+      </c>
+      <c r="BI5" t="n" s="0">
+        <v>1900.0</v>
+      </c>
+      <c r="BJ5" t="n" s="0">
+        <v>2100.0</v>
+      </c>
+      <c r="BK5" t="n" s="0">
+        <v>2000.0</v>
+      </c>
+      <c r="BL5" t="n" s="0">
+        <v>2400.0</v>
+      </c>
+      <c r="BM5" t="n" s="0">
+        <v>2400.0</v>
+      </c>
+      <c r="BN5" t="n" s="0">
+        <v>2800.0</v>
+      </c>
+      <c r="BO5" t="n" s="0">
+        <v>2400.0</v>
+      </c>
+      <c r="BP5" t="n" s="0">
+        <v>2600.0</v>
+      </c>
+      <c r="BQ5" t="n" s="0">
+        <v>1800.0</v>
+      </c>
+      <c r="BR5" t="n" s="0">
+        <v>2300.0</v>
+      </c>
+      <c r="BS5" t="n" s="0">
+        <v>2600.0</v>
+      </c>
+      <c r="BT5" t="n" s="0">
+        <v>2400.0</v>
+      </c>
+      <c r="BU5" t="n" s="0">
+        <v>2800.0</v>
+      </c>
+      <c r="BV5" t="n" s="0">
+        <v>1700.0</v>
+      </c>
+      <c r="BW5" t="n" s="0">
+        <v>2200.0</v>
+      </c>
+      <c r="BX5" t="n" s="0">
+        <v>1900.0</v>
+      </c>
+      <c r="BY5" t="n" s="0">
+        <v>2200.0</v>
+      </c>
+      <c r="BZ5" t="n" s="0">
+        <v>2300.0</v>
+      </c>
+      <c r="CA5" t="n" s="0">
+        <v>2100.0</v>
+      </c>
+      <c r="CB5" t="n" s="0">
+        <v>2100.0</v>
+      </c>
+      <c r="CC5" t="n" s="0">
+        <v>1900.0</v>
+      </c>
+      <c r="CD5" t="n" s="0">
+        <v>2300.0</v>
+      </c>
+      <c r="CE5" t="n" s="0">
+        <v>2600.0</v>
+      </c>
+      <c r="CF5" t="n" s="0">
+        <v>2400.0</v>
+      </c>
+      <c r="CG5" t="n" s="0">
+        <v>2500.0</v>
+      </c>
+      <c r="CH5" t="n" s="0">
+        <v>2100.0</v>
+      </c>
+      <c r="CI5" t="n" s="0">
+        <v>2200.0</v>
+      </c>
+      <c r="CJ5" t="n" s="0">
+        <v>2000.0</v>
+      </c>
+      <c r="CK5" t="n" s="0">
+        <v>1800.0</v>
+      </c>
+      <c r="CL5" t="n" s="0">
+        <v>2300.0</v>
+      </c>
+      <c r="CM5" t="n" s="0">
+        <v>2600.0</v>
+      </c>
+      <c r="CN5" t="n" s="0">
+        <v>2500.0</v>
+      </c>
+      <c r="CO5" t="n" s="0">
+        <v>2400.0</v>
+      </c>
+      <c r="CP5" t="n" s="0">
+        <v>2200.0</v>
+      </c>
+      <c r="CQ5" t="n" s="0">
+        <v>2000.0</v>
+      </c>
+      <c r="CR5" t="n" s="0">
+        <v>2300.0</v>
+      </c>
+      <c r="CS5" t="n" s="0">
+        <v>2500.0</v>
+      </c>
+      <c r="CT5" t="n" s="0">
+        <v>1800.0</v>
+      </c>
+      <c r="CU5" t="n" s="0">
+        <v>1900.0</v>
+      </c>
+      <c r="CV5" t="n" s="0">
+        <v>1900.0</v>
+      </c>
+      <c r="CW5" t="n" s="0">
+        <v>2300.0</v>
+      </c>
+      <c r="CX5" t="n" s="0">
+        <v>2500.0</v>
       </c>
     </row>
     <row r="6">
@@ -1347,154 +2247,304 @@
         <v>100.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>46400.0</v>
+        <v>48900.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>56000.0</v>
+        <v>45900.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>46000.0</v>
+        <v>46200.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>93300.0</v>
+        <v>79700.0</v>
       </c>
       <c r="G6" t="n" s="0">
-        <v>76400.0</v>
+        <v>94500.0</v>
       </c>
       <c r="H6" t="n" s="0">
-        <v>45100.0</v>
+        <v>76000.0</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>81100.0</v>
+        <v>45800.0</v>
       </c>
       <c r="J6" t="n" s="0">
-        <v>93900.0</v>
+        <v>92200.0</v>
       </c>
       <c r="K6" t="n" s="0">
-        <v>84600.0</v>
+        <v>91400.0</v>
       </c>
       <c r="L6" t="n" s="0">
-        <v>52000.0</v>
+        <v>89300.0</v>
       </c>
       <c r="M6" t="n" s="0">
-        <v>78900.0</v>
+        <v>45700.0</v>
       </c>
       <c r="N6" t="n" s="0">
-        <v>104200.0</v>
+        <v>54000.0</v>
       </c>
       <c r="O6" t="n" s="0">
-        <v>47200.0</v>
+        <v>51300.0</v>
       </c>
       <c r="P6" t="n" s="0">
-        <v>20700.0</v>
+        <v>12500.0</v>
       </c>
       <c r="Q6" t="n" s="0">
-        <v>11600.0</v>
+        <v>11300.0</v>
       </c>
       <c r="R6" t="n" s="0">
+        <v>12400.0</v>
+      </c>
+      <c r="S6" t="n" s="0">
+        <v>22600.0</v>
+      </c>
+      <c r="T6" t="n" s="0">
+        <v>21400.0</v>
+      </c>
+      <c r="U6" t="n" s="0">
         <v>22300.0</v>
       </c>
-      <c r="S6" t="n" s="0">
-        <v>13000.0</v>
-      </c>
-      <c r="T6" t="n" s="0">
-        <v>13200.0</v>
-      </c>
-      <c r="U6" t="n" s="0">
-        <v>23600.0</v>
-      </c>
       <c r="V6" t="n" s="0">
-        <v>22800.0</v>
+        <v>19000.0</v>
       </c>
       <c r="W6" t="n" s="0">
-        <v>22500.0</v>
+        <v>21600.0</v>
       </c>
       <c r="X6" t="n" s="0">
-        <v>23100.0</v>
+        <v>21900.0</v>
       </c>
       <c r="Y6" t="n" s="0">
-        <v>22300.0</v>
+        <v>20000.0</v>
       </c>
       <c r="Z6" t="n" s="0">
-        <v>33500.0</v>
+        <v>24600.0</v>
       </c>
       <c r="AA6" t="n" s="0">
-        <v>76400.0</v>
+        <v>27000.0</v>
       </c>
       <c r="AB6" t="n" s="0">
-        <v>22200.0</v>
+        <v>22000.0</v>
       </c>
       <c r="AC6" t="n" s="0">
-        <v>10000.0</v>
+        <v>106300.0</v>
       </c>
       <c r="AD6" t="n" s="0">
-        <v>6700.0</v>
+        <v>11500.0</v>
       </c>
       <c r="AE6" t="n" s="0">
+        <v>8100.0</v>
+      </c>
+      <c r="AF6" t="n" s="0">
+        <v>9200.0</v>
+      </c>
+      <c r="AG6" t="n" s="0">
+        <v>8500.0</v>
+      </c>
+      <c r="AH6" t="n" s="0">
+        <v>8000.0</v>
+      </c>
+      <c r="AI6" t="n" s="0">
+        <v>8900.0</v>
+      </c>
+      <c r="AJ6" t="n" s="0">
+        <v>8100.0</v>
+      </c>
+      <c r="AK6" t="n" s="0">
+        <v>7500.0</v>
+      </c>
+      <c r="AL6" t="n" s="0">
+        <v>7200.0</v>
+      </c>
+      <c r="AM6" t="n" s="0">
+        <v>7300.0</v>
+      </c>
+      <c r="AN6" t="n" s="0">
+        <v>6300.0</v>
+      </c>
+      <c r="AO6" t="n" s="0">
+        <v>8800.0</v>
+      </c>
+      <c r="AP6" t="n" s="0">
+        <v>8100.0</v>
+      </c>
+      <c r="AQ6" t="n" s="0">
+        <v>8000.0</v>
+      </c>
+      <c r="AR6" t="n" s="0">
+        <v>6200.0</v>
+      </c>
+      <c r="AS6" t="n" s="0">
+        <v>8400.0</v>
+      </c>
+      <c r="AT6" t="n" s="0">
+        <v>6400.0</v>
+      </c>
+      <c r="AU6" t="n" s="0">
+        <v>6200.0</v>
+      </c>
+      <c r="AV6" t="n" s="0">
+        <v>8300.0</v>
+      </c>
+      <c r="AW6" t="n" s="0">
+        <v>8300.0</v>
+      </c>
+      <c r="AX6" t="n" s="0">
+        <v>8200.0</v>
+      </c>
+      <c r="AY6" t="n" s="0">
+        <v>7100.0</v>
+      </c>
+      <c r="AZ6" t="n" s="0">
         <v>6800.0</v>
       </c>
-      <c r="AF6" t="n" s="0">
+      <c r="BA6" t="n" s="0">
+        <v>6000.0</v>
+      </c>
+      <c r="BB6" t="n" s="0">
+        <v>6400.0</v>
+      </c>
+      <c r="BC6" t="n" s="0">
         <v>8000.0</v>
       </c>
-      <c r="AG6" t="n" s="0">
+      <c r="BD6" t="n" s="0">
+        <v>8300.0</v>
+      </c>
+      <c r="BE6" t="n" s="0">
+        <v>6000.0</v>
+      </c>
+      <c r="BF6" t="n" s="0">
+        <v>8500.0</v>
+      </c>
+      <c r="BG6" t="n" s="0">
+        <v>5400.0</v>
+      </c>
+      <c r="BH6" t="n" s="0">
+        <v>5700.0</v>
+      </c>
+      <c r="BI6" t="n" s="0">
+        <v>5900.0</v>
+      </c>
+      <c r="BJ6" t="n" s="0">
+        <v>5300.0</v>
+      </c>
+      <c r="BK6" t="n" s="0">
+        <v>6400.0</v>
+      </c>
+      <c r="BL6" t="n" s="0">
+        <v>9000.0</v>
+      </c>
+      <c r="BM6" t="n" s="0">
+        <v>8200.0</v>
+      </c>
+      <c r="BN6" t="n" s="0">
+        <v>7700.0</v>
+      </c>
+      <c r="BO6" t="n" s="0">
+        <v>8900.0</v>
+      </c>
+      <c r="BP6" t="n" s="0">
+        <v>8200.0</v>
+      </c>
+      <c r="BQ6" t="n" s="0">
+        <v>5700.0</v>
+      </c>
+      <c r="BR6" t="n" s="0">
+        <v>7000.0</v>
+      </c>
+      <c r="BS6" t="n" s="0">
+        <v>6600.0</v>
+      </c>
+      <c r="BT6" t="n" s="0">
+        <v>8200.0</v>
+      </c>
+      <c r="BU6" t="n" s="0">
         <v>8400.0</v>
       </c>
-      <c r="AH6" t="n" s="0">
+      <c r="BV6" t="n" s="0">
         <v>6300.0</v>
       </c>
-      <c r="AI6" t="n" s="0">
+      <c r="BW6" t="n" s="0">
+        <v>5600.0</v>
+      </c>
+      <c r="BX6" t="n" s="0">
+        <v>6100.0</v>
+      </c>
+      <c r="BY6" t="n" s="0">
+        <v>6000.0</v>
+      </c>
+      <c r="BZ6" t="n" s="0">
+        <v>8300.0</v>
+      </c>
+      <c r="CA6" t="n" s="0">
+        <v>5200.0</v>
+      </c>
+      <c r="CB6" t="n" s="0">
+        <v>5800.0</v>
+      </c>
+      <c r="CC6" t="n" s="0">
+        <v>5600.0</v>
+      </c>
+      <c r="CD6" t="n" s="0">
+        <v>7900.0</v>
+      </c>
+      <c r="CE6" t="n" s="0">
+        <v>8600.0</v>
+      </c>
+      <c r="CF6" t="n" s="0">
+        <v>8700.0</v>
+      </c>
+      <c r="CG6" t="n" s="0">
+        <v>8000.0</v>
+      </c>
+      <c r="CH6" t="n" s="0">
+        <v>6200.0</v>
+      </c>
+      <c r="CI6" t="n" s="0">
+        <v>6400.0</v>
+      </c>
+      <c r="CJ6" t="n" s="0">
+        <v>5800.0</v>
+      </c>
+      <c r="CK6" t="n" s="0">
+        <v>5800.0</v>
+      </c>
+      <c r="CL6" t="n" s="0">
         <v>8400.0</v>
       </c>
-      <c r="AJ6" t="n" s="0">
-        <v>8200.0</v>
-      </c>
-      <c r="AK6" t="n" s="0">
-        <v>6800.0</v>
-      </c>
-      <c r="AL6" t="n" s="0">
-        <v>7900.0</v>
-      </c>
-      <c r="AM6" t="n" s="0">
-        <v>11100.0</v>
-      </c>
-      <c r="AN6" t="n" s="0">
-        <v>6800.0</v>
-      </c>
-      <c r="AO6" t="n" s="0">
+      <c r="CM6" t="n" s="0">
+        <v>8000.0</v>
+      </c>
+      <c r="CN6" t="n" s="0">
+        <v>7300.0</v>
+      </c>
+      <c r="CO6" t="n" s="0">
+        <v>5500.0</v>
+      </c>
+      <c r="CP6" t="n" s="0">
+        <v>6100.0</v>
+      </c>
+      <c r="CQ6" t="n" s="0">
+        <v>6300.0</v>
+      </c>
+      <c r="CR6" t="n" s="0">
         <v>8100.0</v>
       </c>
-      <c r="AP6" t="n" s="0">
-        <v>8600.0</v>
-      </c>
-      <c r="AQ6" t="n" s="0">
-        <v>8600.0</v>
-      </c>
-      <c r="AR6" t="n" s="0">
-        <v>8800.0</v>
-      </c>
-      <c r="AS6" t="n" s="0">
-        <v>8800.0</v>
-      </c>
-      <c r="AT6" t="n" s="0">
+      <c r="CS6" t="n" s="0">
+        <v>8700.0</v>
+      </c>
+      <c r="CT6" t="n" s="0">
+        <v>6300.0</v>
+      </c>
+      <c r="CU6" t="n" s="0">
+        <v>6100.0</v>
+      </c>
+      <c r="CV6" t="n" s="0">
+        <v>6300.0</v>
+      </c>
+      <c r="CW6" t="n" s="0">
+        <v>5900.0</v>
+      </c>
+      <c r="CX6" t="n" s="0">
         <v>8500.0</v>
-      </c>
-      <c r="AU6" t="n" s="0">
-        <v>8500.0</v>
-      </c>
-      <c r="AV6" t="n" s="0">
-        <v>8500.0</v>
-      </c>
-      <c r="AW6" t="n" s="0">
-        <v>8500.0</v>
-      </c>
-      <c r="AX6" t="n" s="0">
-        <v>8800.0</v>
-      </c>
-      <c r="AY6" t="n" s="0">
-        <v>8900.0</v>
-      </c>
-      <c r="AZ6" t="n" s="0">
-        <v>8600.0</v>
       </c>
     </row>
     <row r="7">
@@ -1505,154 +2555,304 @@
         <v>100.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>47000.0</v>
+        <v>48200.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>59700.0</v>
+        <v>54000.0</v>
       </c>
       <c r="E7" t="n" s="0">
-        <v>46100.0</v>
+        <v>44600.0</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>97100.0</v>
+        <v>82300.0</v>
       </c>
       <c r="G7" t="n" s="0">
-        <v>76300.0</v>
+        <v>92200.0</v>
       </c>
       <c r="H7" t="n" s="0">
-        <v>71400.0</v>
+        <v>74800.0</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>80300.0</v>
+        <v>44800.0</v>
       </c>
       <c r="J7" t="n" s="0">
-        <v>99700.0</v>
+        <v>95300.0</v>
       </c>
       <c r="K7" t="n" s="0">
-        <v>93100.0</v>
+        <v>98300.0</v>
       </c>
       <c r="L7" t="n" s="0">
-        <v>50200.0</v>
+        <v>90600.0</v>
       </c>
       <c r="M7" t="n" s="0">
-        <v>76000.0</v>
+        <v>44800.0</v>
       </c>
       <c r="N7" t="n" s="0">
-        <v>97500.0</v>
+        <v>77100.0</v>
       </c>
       <c r="O7" t="n" s="0">
-        <v>37600.0</v>
+        <v>47500.0</v>
       </c>
       <c r="P7" t="n" s="0">
-        <v>16100.0</v>
+        <v>13500.0</v>
       </c>
       <c r="Q7" t="n" s="0">
-        <v>11100.0</v>
+        <v>11000.0</v>
       </c>
       <c r="R7" t="n" s="0">
-        <v>22600.0</v>
+        <v>11500.0</v>
       </c>
       <c r="S7" t="n" s="0">
-        <v>11200.0</v>
+        <v>21700.0</v>
       </c>
       <c r="T7" t="n" s="0">
-        <v>11300.0</v>
+        <v>21900.0</v>
       </c>
       <c r="U7" t="n" s="0">
-        <v>23000.0</v>
+        <v>21800.0</v>
       </c>
       <c r="V7" t="n" s="0">
-        <v>22700.0</v>
+        <v>19200.0</v>
       </c>
       <c r="W7" t="n" s="0">
-        <v>21600.0</v>
+        <v>21700.0</v>
       </c>
       <c r="X7" t="n" s="0">
-        <v>34900.0</v>
+        <v>43800.0</v>
       </c>
       <c r="Y7" t="n" s="0">
-        <v>22500.0</v>
+        <v>17900.0</v>
       </c>
       <c r="Z7" t="n" s="0">
-        <v>66100.0</v>
+        <v>23500.0</v>
       </c>
       <c r="AA7" t="n" s="0">
-        <v>17600.0</v>
+        <v>21500.0</v>
       </c>
       <c r="AB7" t="n" s="0">
-        <v>10100.0</v>
+        <v>22100.0</v>
       </c>
       <c r="AC7" t="n" s="0">
-        <v>9000.0</v>
+        <v>69700.0</v>
       </c>
       <c r="AD7" t="n" s="0">
+        <v>29100.0</v>
+      </c>
+      <c r="AE7" t="n" s="0">
+        <v>70100.0</v>
+      </c>
+      <c r="AF7" t="n" s="0">
+        <v>10600.0</v>
+      </c>
+      <c r="AG7" t="n" s="0">
+        <v>8200.0</v>
+      </c>
+      <c r="AH7" t="n" s="0">
+        <v>54400.0</v>
+      </c>
+      <c r="AI7" t="n" s="0">
+        <v>8300.0</v>
+      </c>
+      <c r="AJ7" t="n" s="0">
+        <v>8500.0</v>
+      </c>
+      <c r="AK7" t="n" s="0">
+        <v>7000.0</v>
+      </c>
+      <c r="AL7" t="n" s="0">
+        <v>6700.0</v>
+      </c>
+      <c r="AM7" t="n" s="0">
+        <v>8400.0</v>
+      </c>
+      <c r="AN7" t="n" s="0">
+        <v>5800.0</v>
+      </c>
+      <c r="AO7" t="n" s="0">
+        <v>8200.0</v>
+      </c>
+      <c r="AP7" t="n" s="0">
+        <v>8800.0</v>
+      </c>
+      <c r="AQ7" t="n" s="0">
+        <v>5700.0</v>
+      </c>
+      <c r="AR7" t="n" s="0">
+        <v>5800.0</v>
+      </c>
+      <c r="AS7" t="n" s="0">
+        <v>7900.0</v>
+      </c>
+      <c r="AT7" t="n" s="0">
+        <v>5800.0</v>
+      </c>
+      <c r="AU7" t="n" s="0">
+        <v>5100.0</v>
+      </c>
+      <c r="AV7" t="n" s="0">
+        <v>8200.0</v>
+      </c>
+      <c r="AW7" t="n" s="0">
+        <v>8300.0</v>
+      </c>
+      <c r="AX7" t="n" s="0">
+        <v>8000.0</v>
+      </c>
+      <c r="AY7" t="n" s="0">
+        <v>6800.0</v>
+      </c>
+      <c r="AZ7" t="n" s="0">
+        <v>5700.0</v>
+      </c>
+      <c r="BA7" t="n" s="0">
+        <v>5600.0</v>
+      </c>
+      <c r="BB7" t="n" s="0">
+        <v>7500.0</v>
+      </c>
+      <c r="BC7" t="n" s="0">
+        <v>8100.0</v>
+      </c>
+      <c r="BD7" t="n" s="0">
+        <v>7900.0</v>
+      </c>
+      <c r="BE7" t="n" s="0">
+        <v>5100.0</v>
+      </c>
+      <c r="BF7" t="n" s="0">
+        <v>8100.0</v>
+      </c>
+      <c r="BG7" t="n" s="0">
+        <v>5200.0</v>
+      </c>
+      <c r="BH7" t="n" s="0">
+        <v>5100.0</v>
+      </c>
+      <c r="BI7" t="n" s="0">
+        <v>6000.0</v>
+      </c>
+      <c r="BJ7" t="n" s="0">
         <v>5500.0</v>
       </c>
-      <c r="AE7" t="n" s="0">
-        <v>6900.0</v>
-      </c>
-      <c r="AF7" t="n" s="0">
+      <c r="BK7" t="n" s="0">
+        <v>5400.0</v>
+      </c>
+      <c r="BL7" t="n" s="0">
+        <v>8800.0</v>
+      </c>
+      <c r="BM7" t="n" s="0">
+        <v>7800.0</v>
+      </c>
+      <c r="BN7" t="n" s="0">
+        <v>7400.0</v>
+      </c>
+      <c r="BO7" t="n" s="0">
+        <v>7700.0</v>
+      </c>
+      <c r="BP7" t="n" s="0">
+        <v>8500.0</v>
+      </c>
+      <c r="BQ7" t="n" s="0">
+        <v>5100.0</v>
+      </c>
+      <c r="BR7" t="n" s="0">
+        <v>6500.0</v>
+      </c>
+      <c r="BS7" t="n" s="0">
+        <v>6600.0</v>
+      </c>
+      <c r="BT7" t="n" s="0">
+        <v>8000.0</v>
+      </c>
+      <c r="BU7" t="n" s="0">
+        <v>8100.0</v>
+      </c>
+      <c r="BV7" t="n" s="0">
+        <v>5700.0</v>
+      </c>
+      <c r="BW7" t="n" s="0">
+        <v>5100.0</v>
+      </c>
+      <c r="BX7" t="n" s="0">
+        <v>6000.0</v>
+      </c>
+      <c r="BY7" t="n" s="0">
+        <v>6000.0</v>
+      </c>
+      <c r="BZ7" t="n" s="0">
+        <v>8000.0</v>
+      </c>
+      <c r="CA7" t="n" s="0">
+        <v>5800.0</v>
+      </c>
+      <c r="CB7" t="n" s="0">
+        <v>5500.0</v>
+      </c>
+      <c r="CC7" t="n" s="0">
+        <v>5000.0</v>
+      </c>
+      <c r="CD7" t="n" s="0">
+        <v>8000.0</v>
+      </c>
+      <c r="CE7" t="n" s="0">
+        <v>8700.0</v>
+      </c>
+      <c r="CF7" t="n" s="0">
+        <v>8000.0</v>
+      </c>
+      <c r="CG7" t="n" s="0">
+        <v>8400.0</v>
+      </c>
+      <c r="CH7" t="n" s="0">
+        <v>6000.0</v>
+      </c>
+      <c r="CI7" t="n" s="0">
+        <v>5700.0</v>
+      </c>
+      <c r="CJ7" t="n" s="0">
+        <v>5200.0</v>
+      </c>
+      <c r="CK7" t="n" s="0">
+        <v>5500.0</v>
+      </c>
+      <c r="CL7" t="n" s="0">
+        <v>8200.0</v>
+      </c>
+      <c r="CM7" t="n" s="0">
+        <v>8500.0</v>
+      </c>
+      <c r="CN7" t="n" s="0">
+        <v>7600.0</v>
+      </c>
+      <c r="CO7" t="n" s="0">
+        <v>5200.0</v>
+      </c>
+      <c r="CP7" t="n" s="0">
+        <v>5300.0</v>
+      </c>
+      <c r="CQ7" t="n" s="0">
+        <v>5700.0</v>
+      </c>
+      <c r="CR7" t="n" s="0">
+        <v>7600.0</v>
+      </c>
+      <c r="CS7" t="n" s="0">
+        <v>8100.0</v>
+      </c>
+      <c r="CT7" t="n" s="0">
+        <v>5500.0</v>
+      </c>
+      <c r="CU7" t="n" s="0">
+        <v>5600.0</v>
+      </c>
+      <c r="CV7" t="n" s="0">
+        <v>5600.0</v>
+      </c>
+      <c r="CW7" t="n" s="0">
+        <v>5500.0</v>
+      </c>
+      <c r="CX7" t="n" s="0">
         <v>7900.0</v>
-      </c>
-      <c r="AG7" t="n" s="0">
-        <v>8300.0</v>
-      </c>
-      <c r="AH7" t="n" s="0">
-        <v>5800.0</v>
-      </c>
-      <c r="AI7" t="n" s="0">
-        <v>8000.0</v>
-      </c>
-      <c r="AJ7" t="n" s="0">
-        <v>8800.0</v>
-      </c>
-      <c r="AK7" t="n" s="0">
-        <v>7200.0</v>
-      </c>
-      <c r="AL7" t="n" s="0">
-        <v>6500.0</v>
-      </c>
-      <c r="AM7" t="n" s="0">
-        <v>11000.0</v>
-      </c>
-      <c r="AN7" t="n" s="0">
-        <v>6000.0</v>
-      </c>
-      <c r="AO7" t="n" s="0">
-        <v>8500.0</v>
-      </c>
-      <c r="AP7" t="n" s="0">
-        <v>8400.0</v>
-      </c>
-      <c r="AQ7" t="n" s="0">
-        <v>8000.0</v>
-      </c>
-      <c r="AR7" t="n" s="0">
-        <v>8300.0</v>
-      </c>
-      <c r="AS7" t="n" s="0">
-        <v>9100.0</v>
-      </c>
-      <c r="AT7" t="n" s="0">
-        <v>8300.0</v>
-      </c>
-      <c r="AU7" t="n" s="0">
-        <v>15300.0</v>
-      </c>
-      <c r="AV7" t="n" s="0">
-        <v>8400.0</v>
-      </c>
-      <c r="AW7" t="n" s="0">
-        <v>8400.0</v>
-      </c>
-      <c r="AX7" t="n" s="0">
-        <v>9000.0</v>
-      </c>
-      <c r="AY7" t="n" s="0">
-        <v>8300.0</v>
-      </c>
-      <c r="AZ7" t="n" s="0">
-        <v>8400.0</v>
       </c>
     </row>
     <row r="8">
@@ -1663,154 +2863,304 @@
         <v>100.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>44700.0</v>
+        <v>45000.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>84200.0</v>
+        <v>60000.0</v>
       </c>
       <c r="E8" t="n" s="0">
-        <v>35400.0</v>
+        <v>36300.0</v>
       </c>
       <c r="F8" t="n" s="0">
-        <v>67200.0</v>
+        <v>78300.0</v>
       </c>
       <c r="G8" t="n" s="0">
-        <v>24500.0</v>
+        <v>31100.0</v>
       </c>
       <c r="H8" t="n" s="0">
-        <v>9900.0</v>
+        <v>13400.0</v>
       </c>
       <c r="I8" t="n" s="0">
-        <v>15300.0</v>
+        <v>9500.0</v>
       </c>
       <c r="J8" t="n" s="0">
-        <v>20600.0</v>
+        <v>17900.0</v>
       </c>
       <c r="K8" t="n" s="0">
-        <v>16800.0</v>
+        <v>17100.0</v>
       </c>
       <c r="L8" t="n" s="0">
-        <v>10500.0</v>
+        <v>17600.0</v>
       </c>
       <c r="M8" t="n" s="0">
-        <v>14100.0</v>
+        <v>10800.0</v>
       </c>
       <c r="N8" t="n" s="0">
         <v>18000.0</v>
       </c>
       <c r="O8" t="n" s="0">
-        <v>15200.0</v>
+        <v>18200.0</v>
       </c>
       <c r="P8" t="n" s="0">
+        <v>9900.0</v>
+      </c>
+      <c r="Q8" t="n" s="0">
+        <v>10300.0</v>
+      </c>
+      <c r="R8" t="n" s="0">
+        <v>8800.0</v>
+      </c>
+      <c r="S8" t="n" s="0">
+        <v>16300.0</v>
+      </c>
+      <c r="T8" t="n" s="0">
+        <v>19200.0</v>
+      </c>
+      <c r="U8" t="n" s="0">
+        <v>16400.0</v>
+      </c>
+      <c r="V8" t="n" s="0">
+        <v>12400.0</v>
+      </c>
+      <c r="W8" t="n" s="0">
+        <v>15000.0</v>
+      </c>
+      <c r="X8" t="n" s="0">
+        <v>11800.0</v>
+      </c>
+      <c r="Y8" t="n" s="0">
+        <v>51700.0</v>
+      </c>
+      <c r="Z8" t="n" s="0">
+        <v>12900.0</v>
+      </c>
+      <c r="AA8" t="n" s="0">
+        <v>17400.0</v>
+      </c>
+      <c r="AB8" t="n" s="0">
+        <v>15000.0</v>
+      </c>
+      <c r="AC8" t="n" s="0">
+        <v>19600.0</v>
+      </c>
+      <c r="AD8" t="n" s="0">
+        <v>19400.0</v>
+      </c>
+      <c r="AE8" t="n" s="0">
+        <v>22600.0</v>
+      </c>
+      <c r="AF8" t="n" s="0">
+        <v>16700.0</v>
+      </c>
+      <c r="AG8" t="n" s="0">
+        <v>17200.0</v>
+      </c>
+      <c r="AH8" t="n" s="0">
         <v>13200.0</v>
       </c>
-      <c r="Q8" t="n" s="0">
-        <v>10100.0</v>
-      </c>
-      <c r="R8" t="n" s="0">
-        <v>17100.0</v>
-      </c>
-      <c r="S8" t="n" s="0">
-        <v>17400.0</v>
-      </c>
-      <c r="T8" t="n" s="0">
-        <v>9900.0</v>
-      </c>
-      <c r="U8" t="n" s="0">
-        <v>17900.0</v>
-      </c>
-      <c r="V8" t="n" s="0">
-        <v>17200.0</v>
-      </c>
-      <c r="W8" t="n" s="0">
-        <v>14200.0</v>
-      </c>
-      <c r="X8" t="n" s="0">
-        <v>18900.0</v>
-      </c>
-      <c r="Y8" t="n" s="0">
-        <v>30100.0</v>
-      </c>
-      <c r="Z8" t="n" s="0">
-        <v>16300.0</v>
-      </c>
-      <c r="AA8" t="n" s="0">
-        <v>31900.0</v>
-      </c>
-      <c r="AB8" t="n" s="0">
-        <v>19600.0</v>
-      </c>
-      <c r="AC8" t="n" s="0">
-        <v>14500.0</v>
-      </c>
-      <c r="AD8" t="n" s="0">
-        <v>10500.0</v>
-      </c>
-      <c r="AE8" t="n" s="0">
-        <v>12300.0</v>
-      </c>
-      <c r="AF8" t="n" s="0">
-        <v>12900.0</v>
-      </c>
-      <c r="AG8" t="n" s="0">
-        <v>13400.0</v>
-      </c>
-      <c r="AH8" t="n" s="0">
-        <v>10600.0</v>
-      </c>
       <c r="AI8" t="n" s="0">
-        <v>15400.0</v>
+        <v>14400.0</v>
       </c>
       <c r="AJ8" t="n" s="0">
-        <v>13600.0</v>
+        <v>161900.0</v>
       </c>
       <c r="AK8" t="n" s="0">
-        <v>10100.0</v>
+        <v>12000.0</v>
       </c>
       <c r="AL8" t="n" s="0">
-        <v>11100.0</v>
+        <v>25300.0</v>
       </c>
       <c r="AM8" t="n" s="0">
-        <v>54400.0</v>
+        <v>13100.0</v>
       </c>
       <c r="AN8" t="n" s="0">
-        <v>10000.0</v>
+        <v>8100.0</v>
       </c>
       <c r="AO8" t="n" s="0">
-        <v>12400.0</v>
+        <v>15300.0</v>
       </c>
       <c r="AP8" t="n" s="0">
-        <v>12000.0</v>
+        <v>12200.0</v>
       </c>
       <c r="AQ8" t="n" s="0">
-        <v>12000.0</v>
+        <v>11900.0</v>
       </c>
       <c r="AR8" t="n" s="0">
-        <v>14200.0</v>
+        <v>8500.0</v>
       </c>
       <c r="AS8" t="n" s="0">
         <v>12500.0</v>
       </c>
       <c r="AT8" t="n" s="0">
+        <v>56200.0</v>
+      </c>
+      <c r="AU8" t="n" s="0">
+        <v>8800.0</v>
+      </c>
+      <c r="AV8" t="n" s="0">
+        <v>17100.0</v>
+      </c>
+      <c r="AW8" t="n" s="0">
+        <v>32300.0</v>
+      </c>
+      <c r="AX8" t="n" s="0">
+        <v>12100.0</v>
+      </c>
+      <c r="AY8" t="n" s="0">
+        <v>11100.0</v>
+      </c>
+      <c r="AZ8" t="n" s="0">
+        <v>9400.0</v>
+      </c>
+      <c r="BA8" t="n" s="0">
+        <v>9400.0</v>
+      </c>
+      <c r="BB8" t="n" s="0">
+        <v>9300.0</v>
+      </c>
+      <c r="BC8" t="n" s="0">
+        <v>13300.0</v>
+      </c>
+      <c r="BD8" t="n" s="0">
+        <v>11900.0</v>
+      </c>
+      <c r="BE8" t="n" s="0">
+        <v>8300.0</v>
+      </c>
+      <c r="BF8" t="n" s="0">
+        <v>12200.0</v>
+      </c>
+      <c r="BG8" t="n" s="0">
+        <v>8400.0</v>
+      </c>
+      <c r="BH8" t="n" s="0">
+        <v>7400.0</v>
+      </c>
+      <c r="BI8" t="n" s="0">
+        <v>8500.0</v>
+      </c>
+      <c r="BJ8" t="n" s="0">
+        <v>7400.0</v>
+      </c>
+      <c r="BK8" t="n" s="0">
+        <v>7500.0</v>
+      </c>
+      <c r="BL8" t="n" s="0">
+        <v>12300.0</v>
+      </c>
+      <c r="BM8" t="n" s="0">
+        <v>12400.0</v>
+      </c>
+      <c r="BN8" t="n" s="0">
+        <v>12700.0</v>
+      </c>
+      <c r="BO8" t="n" s="0">
+        <v>11600.0</v>
+      </c>
+      <c r="BP8" t="n" s="0">
+        <v>13200.0</v>
+      </c>
+      <c r="BQ8" t="n" s="0">
+        <v>8600.0</v>
+      </c>
+      <c r="BR8" t="n" s="0">
+        <v>8800.0</v>
+      </c>
+      <c r="BS8" t="n" s="0">
+        <v>8800.0</v>
+      </c>
+      <c r="BT8" t="n" s="0">
+        <v>11800.0</v>
+      </c>
+      <c r="BU8" t="n" s="0">
+        <v>12100.0</v>
+      </c>
+      <c r="BV8" t="n" s="0">
+        <v>8700.0</v>
+      </c>
+      <c r="BW8" t="n" s="0">
+        <v>8000.0</v>
+      </c>
+      <c r="BX8" t="n" s="0">
+        <v>7500.0</v>
+      </c>
+      <c r="BY8" t="n" s="0">
+        <v>8700.0</v>
+      </c>
+      <c r="BZ8" t="n" s="0">
+        <v>12300.0</v>
+      </c>
+      <c r="CA8" t="n" s="0">
+        <v>8100.0</v>
+      </c>
+      <c r="CB8" t="n" s="0">
+        <v>8500.0</v>
+      </c>
+      <c r="CC8" t="n" s="0">
+        <v>7500.0</v>
+      </c>
+      <c r="CD8" t="n" s="0">
+        <v>11200.0</v>
+      </c>
+      <c r="CE8" t="n" s="0">
+        <v>11000.0</v>
+      </c>
+      <c r="CF8" t="n" s="0">
+        <v>11900.0</v>
+      </c>
+      <c r="CG8" t="n" s="0">
+        <v>12400.0</v>
+      </c>
+      <c r="CH8" t="n" s="0">
+        <v>9400.0</v>
+      </c>
+      <c r="CI8" t="n" s="0">
+        <v>8000.0</v>
+      </c>
+      <c r="CJ8" t="n" s="0">
+        <v>6600.0</v>
+      </c>
+      <c r="CK8" t="n" s="0">
+        <v>12200.0</v>
+      </c>
+      <c r="CL8" t="n" s="0">
+        <v>11400.0</v>
+      </c>
+      <c r="CM8" t="n" s="0">
         <v>12000.0</v>
       </c>
-      <c r="AU8" t="n" s="0">
-        <v>13000.0</v>
-      </c>
-      <c r="AV8" t="n" s="0">
-        <v>12400.0</v>
-      </c>
-      <c r="AW8" t="n" s="0">
-        <v>12800.0</v>
-      </c>
-      <c r="AX8" t="n" s="0">
-        <v>17200.0</v>
-      </c>
-      <c r="AY8" t="n" s="0">
-        <v>23400.0</v>
-      </c>
-      <c r="AZ8" t="n" s="0">
+      <c r="CN8" t="n" s="0">
+        <v>9500.0</v>
+      </c>
+      <c r="CO8" t="n" s="0">
+        <v>8100.0</v>
+      </c>
+      <c r="CP8" t="n" s="0">
+        <v>8600.0</v>
+      </c>
+      <c r="CQ8" t="n" s="0">
+        <v>8500.0</v>
+      </c>
+      <c r="CR8" t="n" s="0">
+        <v>11100.0</v>
+      </c>
+      <c r="CS8" t="n" s="0">
         <v>11900.0</v>
+      </c>
+      <c r="CT8" t="n" s="0">
+        <v>9100.0</v>
+      </c>
+      <c r="CU8" t="n" s="0">
+        <v>7600.0</v>
+      </c>
+      <c r="CV8" t="n" s="0">
+        <v>7500.0</v>
+      </c>
+      <c r="CW8" t="n" s="0">
+        <v>9100.0</v>
+      </c>
+      <c r="CX8" t="n" s="0">
+        <v>12300.0</v>
       </c>
     </row>
     <row r="9">
@@ -1821,154 +3171,304 @@
         <v>100.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>42700.0</v>
+        <v>42200.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>87800.0</v>
+        <v>59600.0</v>
       </c>
       <c r="E9" t="n" s="0">
-        <v>72300.0</v>
+        <v>32900.0</v>
       </c>
       <c r="F9" t="n" s="0">
-        <v>74000.0</v>
+        <v>283500.0</v>
       </c>
       <c r="G9" t="n" s="0">
-        <v>28500.0</v>
+        <v>46400.0</v>
       </c>
       <c r="H9" t="n" s="0">
+        <v>13300.0</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>8600.0</v>
+      </c>
+      <c r="J9" t="n" s="0">
+        <v>17600.0</v>
+      </c>
+      <c r="K9" t="n" s="0">
+        <v>19500.0</v>
+      </c>
+      <c r="L9" t="n" s="0">
+        <v>18300.0</v>
+      </c>
+      <c r="M9" t="n" s="0">
+        <v>8400.0</v>
+      </c>
+      <c r="N9" t="n" s="0">
+        <v>16600.0</v>
+      </c>
+      <c r="O9" t="n" s="0">
+        <v>17600.0</v>
+      </c>
+      <c r="P9" t="n" s="0">
+        <v>9000.0</v>
+      </c>
+      <c r="Q9" t="n" s="0">
+        <v>9400.0</v>
+      </c>
+      <c r="R9" t="n" s="0">
+        <v>8600.0</v>
+      </c>
+      <c r="S9" t="n" s="0">
+        <v>16600.0</v>
+      </c>
+      <c r="T9" t="n" s="0">
+        <v>19300.0</v>
+      </c>
+      <c r="U9" t="n" s="0">
+        <v>16900.0</v>
+      </c>
+      <c r="V9" t="n" s="0">
+        <v>13000.0</v>
+      </c>
+      <c r="W9" t="n" s="0">
+        <v>15600.0</v>
+      </c>
+      <c r="X9" t="n" s="0">
+        <v>12200.0</v>
+      </c>
+      <c r="Y9" t="n" s="0">
+        <v>58100.0</v>
+      </c>
+      <c r="Z9" t="n" s="0">
+        <v>13500.0</v>
+      </c>
+      <c r="AA9" t="n" s="0">
+        <v>19000.0</v>
+      </c>
+      <c r="AB9" t="n" s="0">
+        <v>14800.0</v>
+      </c>
+      <c r="AC9" t="n" s="0">
+        <v>24000.0</v>
+      </c>
+      <c r="AD9" t="n" s="0">
+        <v>18800.0</v>
+      </c>
+      <c r="AE9" t="n" s="0">
+        <v>15600.0</v>
+      </c>
+      <c r="AF9" t="n" s="0">
+        <v>16300.0</v>
+      </c>
+      <c r="AG9" t="n" s="0">
+        <v>16600.0</v>
+      </c>
+      <c r="AH9" t="n" s="0">
+        <v>19200.0</v>
+      </c>
+      <c r="AI9" t="n" s="0">
+        <v>13100.0</v>
+      </c>
+      <c r="AJ9" t="n" s="0">
+        <v>54200.0</v>
+      </c>
+      <c r="AK9" t="n" s="0">
+        <v>10400.0</v>
+      </c>
+      <c r="AL9" t="n" s="0">
+        <v>14900.0</v>
+      </c>
+      <c r="AM9" t="n" s="0">
+        <v>12200.0</v>
+      </c>
+      <c r="AN9" t="n" s="0">
+        <v>8000.0</v>
+      </c>
+      <c r="AO9" t="n" s="0">
+        <v>14200.0</v>
+      </c>
+      <c r="AP9" t="n" s="0">
+        <v>12700.0</v>
+      </c>
+      <c r="AQ9" t="n" s="0">
+        <v>8700.0</v>
+      </c>
+      <c r="AR9" t="n" s="0">
+        <v>9000.0</v>
+      </c>
+      <c r="AS9" t="n" s="0">
+        <v>12900.0</v>
+      </c>
+      <c r="AT9" t="n" s="0">
+        <v>9700.0</v>
+      </c>
+      <c r="AU9" t="n" s="0">
+        <v>8600.0</v>
+      </c>
+      <c r="AV9" t="n" s="0">
+        <v>11700.0</v>
+      </c>
+      <c r="AW9" t="n" s="0">
+        <v>12400.0</v>
+      </c>
+      <c r="AX9" t="n" s="0">
+        <v>13000.0</v>
+      </c>
+      <c r="AY9" t="n" s="0">
+        <v>11000.0</v>
+      </c>
+      <c r="AZ9" t="n" s="0">
+        <v>8600.0</v>
+      </c>
+      <c r="BA9" t="n" s="0">
+        <v>8600.0</v>
+      </c>
+      <c r="BB9" t="n" s="0">
+        <v>8800.0</v>
+      </c>
+      <c r="BC9" t="n" s="0">
+        <v>13400.0</v>
+      </c>
+      <c r="BD9" t="n" s="0">
+        <v>11800.0</v>
+      </c>
+      <c r="BE9" t="n" s="0">
+        <v>8200.0</v>
+      </c>
+      <c r="BF9" t="n" s="0">
+        <v>13500.0</v>
+      </c>
+      <c r="BG9" t="n" s="0">
+        <v>8000.0</v>
+      </c>
+      <c r="BH9" t="n" s="0">
+        <v>7400.0</v>
+      </c>
+      <c r="BI9" t="n" s="0">
+        <v>8100.0</v>
+      </c>
+      <c r="BJ9" t="n" s="0">
+        <v>7200.0</v>
+      </c>
+      <c r="BK9" t="n" s="0">
         <v>9300.0</v>
       </c>
-      <c r="I9" t="n" s="0">
-        <v>14300.0</v>
-      </c>
-      <c r="J9" t="n" s="0">
-        <v>17800.0</v>
-      </c>
-      <c r="K9" t="n" s="0">
-        <v>16600.0</v>
-      </c>
-      <c r="L9" t="n" s="0">
-        <v>10200.0</v>
-      </c>
-      <c r="M9" t="n" s="0">
-        <v>14800.0</v>
-      </c>
-      <c r="N9" t="n" s="0">
-        <v>16800.0</v>
-      </c>
-      <c r="O9" t="n" s="0">
-        <v>14000.0</v>
-      </c>
-      <c r="P9" t="n" s="0">
-        <v>21000.0</v>
-      </c>
-      <c r="Q9" t="n" s="0">
-        <v>9600.0</v>
-      </c>
-      <c r="R9" t="n" s="0">
-        <v>17900.0</v>
-      </c>
-      <c r="S9" t="n" s="0">
-        <v>9300.0</v>
-      </c>
-      <c r="T9" t="n" s="0">
-        <v>8900.0</v>
-      </c>
-      <c r="U9" t="n" s="0">
-        <v>17300.0</v>
-      </c>
-      <c r="V9" t="n" s="0">
-        <v>20400.0</v>
-      </c>
-      <c r="W9" t="n" s="0">
-        <v>14300.0</v>
-      </c>
-      <c r="X9" t="n" s="0">
-        <v>18300.0</v>
-      </c>
-      <c r="Y9" t="n" s="0">
-        <v>20300.0</v>
-      </c>
-      <c r="Z9" t="n" s="0">
-        <v>17100.0</v>
-      </c>
-      <c r="AA9" t="n" s="0">
-        <v>13800.0</v>
-      </c>
-      <c r="AB9" t="n" s="0">
-        <v>26000.0</v>
-      </c>
-      <c r="AC9" t="n" s="0">
-        <v>23100.0</v>
-      </c>
-      <c r="AD9" t="n" s="0">
-        <v>10300.0</v>
-      </c>
-      <c r="AE9" t="n" s="0">
-        <v>14800.0</v>
-      </c>
-      <c r="AF9" t="n" s="0">
-        <v>16900.0</v>
-      </c>
-      <c r="AG9" t="n" s="0">
-        <v>17200.0</v>
-      </c>
-      <c r="AH9" t="n" s="0">
-        <v>8900.0</v>
-      </c>
-      <c r="AI9" t="n" s="0">
-        <v>32200.0</v>
-      </c>
-      <c r="AJ9" t="n" s="0">
-        <v>22900.0</v>
-      </c>
-      <c r="AK9" t="n" s="0">
-        <v>14100.0</v>
-      </c>
-      <c r="AL9" t="n" s="0">
-        <v>15800.0</v>
-      </c>
-      <c r="AM9" t="n" s="0">
-        <v>24300.0</v>
-      </c>
-      <c r="AN9" t="n" s="0">
+      <c r="BL9" t="n" s="0">
+        <v>12700.0</v>
+      </c>
+      <c r="BM9" t="n" s="0">
+        <v>12800.0</v>
+      </c>
+      <c r="BN9" t="n" s="0">
+        <v>12800.0</v>
+      </c>
+      <c r="BO9" t="n" s="0">
+        <v>11900.0</v>
+      </c>
+      <c r="BP9" t="n" s="0">
+        <v>12700.0</v>
+      </c>
+      <c r="BQ9" t="n" s="0">
+        <v>8300.0</v>
+      </c>
+      <c r="BR9" t="n" s="0">
+        <v>8800.0</v>
+      </c>
+      <c r="BS9" t="n" s="0">
+        <v>8000.0</v>
+      </c>
+      <c r="BT9" t="n" s="0">
+        <v>11600.0</v>
+      </c>
+      <c r="BU9" t="n" s="0">
+        <v>11500.0</v>
+      </c>
+      <c r="BV9" t="n" s="0">
+        <v>9400.0</v>
+      </c>
+      <c r="BW9" t="n" s="0">
+        <v>7500.0</v>
+      </c>
+      <c r="BX9" t="n" s="0">
+        <v>7400.0</v>
+      </c>
+      <c r="BY9" t="n" s="0">
+        <v>8700.0</v>
+      </c>
+      <c r="BZ9" t="n" s="0">
+        <v>12300.0</v>
+      </c>
+      <c r="CA9" t="n" s="0">
+        <v>8000.0</v>
+      </c>
+      <c r="CB9" t="n" s="0">
+        <v>8600.0</v>
+      </c>
+      <c r="CC9" t="n" s="0">
+        <v>7200.0</v>
+      </c>
+      <c r="CD9" t="n" s="0">
+        <v>11300.0</v>
+      </c>
+      <c r="CE9" t="n" s="0">
+        <v>11100.0</v>
+      </c>
+      <c r="CF9" t="n" s="0">
+        <v>11800.0</v>
+      </c>
+      <c r="CG9" t="n" s="0">
+        <v>11700.0</v>
+      </c>
+      <c r="CH9" t="n" s="0">
+        <v>10500.0</v>
+      </c>
+      <c r="CI9" t="n" s="0">
+        <v>7700.0</v>
+      </c>
+      <c r="CJ9" t="n" s="0">
+        <v>6500.0</v>
+      </c>
+      <c r="CK9" t="n" s="0">
+        <v>9800.0</v>
+      </c>
+      <c r="CL9" t="n" s="0">
+        <v>11400.0</v>
+      </c>
+      <c r="CM9" t="n" s="0">
+        <v>11500.0</v>
+      </c>
+      <c r="CN9" t="n" s="0">
+        <v>9500.0</v>
+      </c>
+      <c r="CO9" t="n" s="0">
+        <v>7700.0</v>
+      </c>
+      <c r="CP9" t="n" s="0">
+        <v>8800.0</v>
+      </c>
+      <c r="CQ9" t="n" s="0">
         <v>8400.0</v>
       </c>
-      <c r="AO9" t="n" s="0">
-        <v>12100.0</v>
-      </c>
-      <c r="AP9" t="n" s="0">
-        <v>11500.0</v>
-      </c>
-      <c r="AQ9" t="n" s="0">
-        <v>11700.0</v>
-      </c>
-      <c r="AR9" t="n" s="0">
-        <v>13400.0</v>
-      </c>
-      <c r="AS9" t="n" s="0">
-        <v>12400.0</v>
-      </c>
-      <c r="AT9" t="n" s="0">
-        <v>11900.0</v>
-      </c>
-      <c r="AU9" t="n" s="0">
-        <v>11200.0</v>
-      </c>
-      <c r="AV9" t="n" s="0">
-        <v>12800.0</v>
-      </c>
-      <c r="AW9" t="n" s="0">
+      <c r="CR9" t="n" s="0">
+        <v>11100.0</v>
+      </c>
+      <c r="CS9" t="n" s="0">
+        <v>12000.0</v>
+      </c>
+      <c r="CT9" t="n" s="0">
+        <v>8700.0</v>
+      </c>
+      <c r="CU9" t="n" s="0">
+        <v>7800.0</v>
+      </c>
+      <c r="CV9" t="n" s="0">
+        <v>7400.0</v>
+      </c>
+      <c r="CW9" t="n" s="0">
+        <v>8300.0</v>
+      </c>
+      <c r="CX9" t="n" s="0">
         <v>12300.0</v>
-      </c>
-      <c r="AX9" t="n" s="0">
-        <v>12300.0</v>
-      </c>
-      <c r="AY9" t="n" s="0">
-        <v>13500.0</v>
-      </c>
-      <c r="AZ9" t="n" s="0">
-        <v>11800.0</v>
       </c>
     </row>
     <row r="10">
@@ -1979,154 +3479,304 @@
         <v>100.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>70000.0</v>
+        <v>42800.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>117400.0</v>
+        <v>82600.0</v>
       </c>
       <c r="E10" t="n" s="0">
-        <v>75300.0</v>
+        <v>72900.0</v>
       </c>
       <c r="F10" t="n" s="0">
+        <v>49200.0</v>
+      </c>
+      <c r="G10" t="n" s="0">
+        <v>25900.0</v>
+      </c>
+      <c r="H10" t="n" s="0">
+        <v>62500.0</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>16700.0</v>
+      </c>
+      <c r="J10" t="n" s="0">
+        <v>17200.0</v>
+      </c>
+      <c r="K10" t="n" s="0">
+        <v>113100.0</v>
+      </c>
+      <c r="L10" t="n" s="0">
+        <v>53500.0</v>
+      </c>
+      <c r="M10" t="n" s="0">
+        <v>10200.0</v>
+      </c>
+      <c r="N10" t="n" s="0">
+        <v>18500.0</v>
+      </c>
+      <c r="O10" t="n" s="0">
+        <v>16800.0</v>
+      </c>
+      <c r="P10" t="n" s="0">
+        <v>10100.0</v>
+      </c>
+      <c r="Q10" t="n" s="0">
+        <v>10700.0</v>
+      </c>
+      <c r="R10" t="n" s="0">
+        <v>10500.0</v>
+      </c>
+      <c r="S10" t="n" s="0">
+        <v>28300.0</v>
+      </c>
+      <c r="T10" t="n" s="0">
         <v>43100.0</v>
       </c>
-      <c r="G10" t="n" s="0">
+      <c r="U10" t="n" s="0">
+        <v>16100.0</v>
+      </c>
+      <c r="V10" t="n" s="0">
+        <v>13700.0</v>
+      </c>
+      <c r="W10" t="n" s="0">
+        <v>15200.0</v>
+      </c>
+      <c r="X10" t="n" s="0">
+        <v>59300.0</v>
+      </c>
+      <c r="Y10" t="n" s="0">
+        <v>29500.0</v>
+      </c>
+      <c r="Z10" t="n" s="0">
+        <v>14400.0</v>
+      </c>
+      <c r="AA10" t="n" s="0">
+        <v>19900.0</v>
+      </c>
+      <c r="AB10" t="n" s="0">
+        <v>30700.0</v>
+      </c>
+      <c r="AC10" t="n" s="0">
+        <v>28000.0</v>
+      </c>
+      <c r="AD10" t="n" s="0">
+        <v>17800.0</v>
+      </c>
+      <c r="AE10" t="n" s="0">
+        <v>16000.0</v>
+      </c>
+      <c r="AF10" t="n" s="0">
+        <v>16300.0</v>
+      </c>
+      <c r="AG10" t="n" s="0">
+        <v>51300.0</v>
+      </c>
+      <c r="AH10" t="n" s="0">
+        <v>14000.0</v>
+      </c>
+      <c r="AI10" t="n" s="0">
+        <v>14500.0</v>
+      </c>
+      <c r="AJ10" t="n" s="0">
+        <v>16300.0</v>
+      </c>
+      <c r="AK10" t="n" s="0">
+        <v>14300.0</v>
+      </c>
+      <c r="AL10" t="n" s="0">
+        <v>14100.0</v>
+      </c>
+      <c r="AM10" t="n" s="0">
+        <v>13500.0</v>
+      </c>
+      <c r="AN10" t="n" s="0">
+        <v>9800.0</v>
+      </c>
+      <c r="AO10" t="n" s="0">
+        <v>16300.0</v>
+      </c>
+      <c r="AP10" t="n" s="0">
+        <v>15400.0</v>
+      </c>
+      <c r="AQ10" t="n" s="0">
+        <v>11000.0</v>
+      </c>
+      <c r="AR10" t="n" s="0">
+        <v>10900.0</v>
+      </c>
+      <c r="AS10" t="n" s="0">
+        <v>16700.0</v>
+      </c>
+      <c r="AT10" t="n" s="0">
+        <v>12800.0</v>
+      </c>
+      <c r="AU10" t="n" s="0">
+        <v>13700.0</v>
+      </c>
+      <c r="AV10" t="n" s="0">
+        <v>31800.0</v>
+      </c>
+      <c r="AW10" t="n" s="0">
+        <v>16200.0</v>
+      </c>
+      <c r="AX10" t="n" s="0">
+        <v>32100.0</v>
+      </c>
+      <c r="AY10" t="n" s="0">
+        <v>14000.0</v>
+      </c>
+      <c r="AZ10" t="n" s="0">
+        <v>10300.0</v>
+      </c>
+      <c r="BA10" t="n" s="0">
         <v>23900.0</v>
       </c>
-      <c r="H10" t="n" s="0">
-        <v>30500.0</v>
-      </c>
-      <c r="I10" t="n" s="0">
-        <v>29500.0</v>
-      </c>
-      <c r="J10" t="n" s="0">
-        <v>18300.0</v>
-      </c>
-      <c r="K10" t="n" s="0">
-        <v>16300.0</v>
-      </c>
-      <c r="L10" t="n" s="0">
+      <c r="BB10" t="n" s="0">
+        <v>16500.0</v>
+      </c>
+      <c r="BC10" t="n" s="0">
+        <v>14900.0</v>
+      </c>
+      <c r="BD10" t="n" s="0">
+        <v>13700.0</v>
+      </c>
+      <c r="BE10" t="n" s="0">
+        <v>15700.0</v>
+      </c>
+      <c r="BF10" t="n" s="0">
+        <v>14300.0</v>
+      </c>
+      <c r="BG10" t="n" s="0">
+        <v>9900.0</v>
+      </c>
+      <c r="BH10" t="n" s="0">
+        <v>9500.0</v>
+      </c>
+      <c r="BI10" t="n" s="0">
+        <v>11800.0</v>
+      </c>
+      <c r="BJ10" t="n" s="0">
+        <v>9800.0</v>
+      </c>
+      <c r="BK10" t="n" s="0">
+        <v>11400.0</v>
+      </c>
+      <c r="BL10" t="n" s="0">
+        <v>15200.0</v>
+      </c>
+      <c r="BM10" t="n" s="0">
+        <v>14600.0</v>
+      </c>
+      <c r="BN10" t="n" s="0">
+        <v>16100.0</v>
+      </c>
+      <c r="BO10" t="n" s="0">
         <v>13500.0</v>
       </c>
-      <c r="M10" t="n" s="0">
-        <v>15000.0</v>
-      </c>
-      <c r="N10" t="n" s="0">
-        <v>15300.0</v>
-      </c>
-      <c r="O10" t="n" s="0">
-        <v>16400.0</v>
-      </c>
-      <c r="P10" t="n" s="0">
-        <v>17000.0</v>
-      </c>
-      <c r="Q10" t="n" s="0">
-        <v>10500.0</v>
-      </c>
-      <c r="R10" t="n" s="0">
-        <v>18400.0</v>
-      </c>
-      <c r="S10" t="n" s="0">
-        <v>10400.0</v>
-      </c>
-      <c r="T10" t="n" s="0">
-        <v>25500.0</v>
-      </c>
-      <c r="U10" t="n" s="0">
-        <v>16300.0</v>
-      </c>
-      <c r="V10" t="n" s="0">
-        <v>17400.0</v>
-      </c>
-      <c r="W10" t="n" s="0">
-        <v>15600.0</v>
-      </c>
-      <c r="X10" t="n" s="0">
-        <v>15800.0</v>
-      </c>
-      <c r="Y10" t="n" s="0">
-        <v>15100.0</v>
-      </c>
-      <c r="Z10" t="n" s="0">
-        <v>19100.0</v>
-      </c>
-      <c r="AA10" t="n" s="0">
+      <c r="BP10" t="n" s="0">
+        <v>14200.0</v>
+      </c>
+      <c r="BQ10" t="n" s="0">
+        <v>12800.0</v>
+      </c>
+      <c r="BR10" t="n" s="0">
+        <v>11800.0</v>
+      </c>
+      <c r="BS10" t="n" s="0">
+        <v>10800.0</v>
+      </c>
+      <c r="BT10" t="n" s="0">
+        <v>17700.0</v>
+      </c>
+      <c r="BU10" t="n" s="0">
+        <v>14900.0</v>
+      </c>
+      <c r="BV10" t="n" s="0">
+        <v>10900.0</v>
+      </c>
+      <c r="BW10" t="n" s="0">
+        <v>11700.0</v>
+      </c>
+      <c r="BX10" t="n" s="0">
+        <v>10200.0</v>
+      </c>
+      <c r="BY10" t="n" s="0">
+        <v>10700.0</v>
+      </c>
+      <c r="BZ10" t="n" s="0">
+        <v>13500.0</v>
+      </c>
+      <c r="CA10" t="n" s="0">
+        <v>11100.0</v>
+      </c>
+      <c r="CB10" t="n" s="0">
+        <v>10900.0</v>
+      </c>
+      <c r="CC10" t="n" s="0">
+        <v>9600.0</v>
+      </c>
+      <c r="CD10" t="n" s="0">
+        <v>13500.0</v>
+      </c>
+      <c r="CE10" t="n" s="0">
+        <v>13000.0</v>
+      </c>
+      <c r="CF10" t="n" s="0">
+        <v>14300.0</v>
+      </c>
+      <c r="CG10" t="n" s="0">
+        <v>14500.0</v>
+      </c>
+      <c r="CH10" t="n" s="0">
+        <v>12800.0</v>
+      </c>
+      <c r="CI10" t="n" s="0">
+        <v>10600.0</v>
+      </c>
+      <c r="CJ10" t="n" s="0">
+        <v>9700.0</v>
+      </c>
+      <c r="CK10" t="n" s="0">
         <v>19300.0</v>
       </c>
-      <c r="AB10" t="n" s="0">
-        <v>18100.0</v>
-      </c>
-      <c r="AC10" t="n" s="0">
-        <v>39300.0</v>
-      </c>
-      <c r="AD10" t="n" s="0">
-        <v>17200.0</v>
-      </c>
-      <c r="AE10" t="n" s="0">
-        <v>14600.0</v>
-      </c>
-      <c r="AF10" t="n" s="0">
-        <v>17000.0</v>
-      </c>
-      <c r="AG10" t="n" s="0">
-        <v>22400.0</v>
-      </c>
-      <c r="AH10" t="n" s="0">
-        <v>11400.0</v>
-      </c>
-      <c r="AI10" t="n" s="0">
-        <v>16500.0</v>
-      </c>
-      <c r="AJ10" t="n" s="0">
-        <v>18100.0</v>
-      </c>
-      <c r="AK10" t="n" s="0">
-        <v>48900.0</v>
-      </c>
-      <c r="AL10" t="n" s="0">
-        <v>14500.0</v>
-      </c>
-      <c r="AM10" t="n" s="0">
-        <v>21500.0</v>
-      </c>
-      <c r="AN10" t="n" s="0">
+      <c r="CL10" t="n" s="0">
+        <v>13700.0</v>
+      </c>
+      <c r="CM10" t="n" s="0">
+        <v>14700.0</v>
+      </c>
+      <c r="CN10" t="n" s="0">
+        <v>12400.0</v>
+      </c>
+      <c r="CO10" t="n" s="0">
+        <v>9600.0</v>
+      </c>
+      <c r="CP10" t="n" s="0">
         <v>10900.0</v>
       </c>
-      <c r="AO10" t="n" s="0">
-        <v>16700.0</v>
-      </c>
-      <c r="AP10" t="n" s="0">
-        <v>13700.0</v>
-      </c>
-      <c r="AQ10" t="n" s="0">
-        <v>15400.0</v>
-      </c>
-      <c r="AR10" t="n" s="0">
-        <v>17100.0</v>
-      </c>
-      <c r="AS10" t="n" s="0">
-        <v>17500.0</v>
-      </c>
-      <c r="AT10" t="n" s="0">
-        <v>16500.0</v>
-      </c>
-      <c r="AU10" t="n" s="0">
-        <v>15200.0</v>
-      </c>
-      <c r="AV10" t="n" s="0">
-        <v>18100.0</v>
-      </c>
-      <c r="AW10" t="n" s="0">
-        <v>46300.0</v>
-      </c>
-      <c r="AX10" t="n" s="0">
-        <v>16700.0</v>
-      </c>
-      <c r="AY10" t="n" s="0">
-        <v>36400.0</v>
-      </c>
-      <c r="AZ10" t="n" s="0">
-        <v>15000.0</v>
+      <c r="CQ10" t="n" s="0">
+        <v>10700.0</v>
+      </c>
+      <c r="CR10" t="n" s="0">
+        <v>13600.0</v>
+      </c>
+      <c r="CS10" t="n" s="0">
+        <v>13500.0</v>
+      </c>
+      <c r="CT10" t="n" s="0">
+        <v>10800.0</v>
+      </c>
+      <c r="CU10" t="n" s="0">
+        <v>9500.0</v>
+      </c>
+      <c r="CV10" t="n" s="0">
+        <v>9400.0</v>
+      </c>
+      <c r="CW10" t="n" s="0">
+        <v>13500.0</v>
+      </c>
+      <c r="CX10" t="n" s="0">
+        <v>14100.0</v>
       </c>
     </row>
     <row r="11">
@@ -2137,154 +3787,304 @@
         <v>100.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>41500.0</v>
+        <v>39500.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>36100.0</v>
+        <v>34400.0</v>
       </c>
       <c r="E11" t="n" s="0">
-        <v>76700.0</v>
+        <v>68600.0</v>
       </c>
       <c r="F11" t="n" s="0">
-        <v>26900.0</v>
+        <v>73600.0</v>
       </c>
       <c r="G11" t="n" s="0">
-        <v>273900.0</v>
+        <v>24300.0</v>
       </c>
       <c r="H11" t="n" s="0">
-        <v>21900.0</v>
+        <v>50700.0</v>
       </c>
       <c r="I11" t="n" s="0">
-        <v>27000.0</v>
+        <v>20800.0</v>
       </c>
       <c r="J11" t="n" s="0">
-        <v>19300.0</v>
+        <v>17200.0</v>
       </c>
       <c r="K11" t="n" s="0">
+        <v>20100.0</v>
+      </c>
+      <c r="L11" t="n" s="0">
+        <v>18100.0</v>
+      </c>
+      <c r="M11" t="n" s="0">
+        <v>9500.0</v>
+      </c>
+      <c r="N11" t="n" s="0">
+        <v>18100.0</v>
+      </c>
+      <c r="O11" t="n" s="0">
         <v>15700.0</v>
       </c>
-      <c r="L11" t="n" s="0">
-        <v>20600.0</v>
-      </c>
-      <c r="M11" t="n" s="0">
-        <v>14900.0</v>
-      </c>
-      <c r="N11" t="n" s="0">
+      <c r="P11" t="n" s="0">
+        <v>10000.0</v>
+      </c>
+      <c r="Q11" t="n" s="0">
+        <v>10400.0</v>
+      </c>
+      <c r="R11" t="n" s="0">
+        <v>10200.0</v>
+      </c>
+      <c r="S11" t="n" s="0">
+        <v>61300.0</v>
+      </c>
+      <c r="T11" t="n" s="0">
+        <v>33100.0</v>
+      </c>
+      <c r="U11" t="n" s="0">
+        <v>15900.0</v>
+      </c>
+      <c r="V11" t="n" s="0">
+        <v>13800.0</v>
+      </c>
+      <c r="W11" t="n" s="0">
+        <v>15000.0</v>
+      </c>
+      <c r="X11" t="n" s="0">
+        <v>123700.0</v>
+      </c>
+      <c r="Y11" t="n" s="0">
+        <v>20200.0</v>
+      </c>
+      <c r="Z11" t="n" s="0">
+        <v>13600.0</v>
+      </c>
+      <c r="AA11" t="n" s="0">
+        <v>16100.0</v>
+      </c>
+      <c r="AB11" t="n" s="0">
+        <v>24100.0</v>
+      </c>
+      <c r="AC11" t="n" s="0">
+        <v>18100.0</v>
+      </c>
+      <c r="AD11" t="n" s="0">
+        <v>17500.0</v>
+      </c>
+      <c r="AE11" t="n" s="0">
+        <v>16400.0</v>
+      </c>
+      <c r="AF11" t="n" s="0">
+        <v>15400.0</v>
+      </c>
+      <c r="AG11" t="n" s="0">
+        <v>31600.0</v>
+      </c>
+      <c r="AH11" t="n" s="0">
+        <v>13200.0</v>
+      </c>
+      <c r="AI11" t="n" s="0">
+        <v>14100.0</v>
+      </c>
+      <c r="AJ11" t="n" s="0">
+        <v>16200.0</v>
+      </c>
+      <c r="AK11" t="n" s="0">
+        <v>13800.0</v>
+      </c>
+      <c r="AL11" t="n" s="0">
+        <v>12800.0</v>
+      </c>
+      <c r="AM11" t="n" s="0">
+        <v>14600.0</v>
+      </c>
+      <c r="AN11" t="n" s="0">
+        <v>9600.0</v>
+      </c>
+      <c r="AO11" t="n" s="0">
+        <v>15300.0</v>
+      </c>
+      <c r="AP11" t="n" s="0">
+        <v>15000.0</v>
+      </c>
+      <c r="AQ11" t="n" s="0">
+        <v>11600.0</v>
+      </c>
+      <c r="AR11" t="n" s="0">
+        <v>10700.0</v>
+      </c>
+      <c r="AS11" t="n" s="0">
+        <v>19100.0</v>
+      </c>
+      <c r="AT11" t="n" s="0">
+        <v>11300.0</v>
+      </c>
+      <c r="AU11" t="n" s="0">
+        <v>9500.0</v>
+      </c>
+      <c r="AV11" t="n" s="0">
+        <v>29400.0</v>
+      </c>
+      <c r="AW11" t="n" s="0">
+        <v>16200.0</v>
+      </c>
+      <c r="AX11" t="n" s="0">
+        <v>23600.0</v>
+      </c>
+      <c r="AY11" t="n" s="0">
+        <v>47600.0</v>
+      </c>
+      <c r="AZ11" t="n" s="0">
+        <v>11100.0</v>
+      </c>
+      <c r="BA11" t="n" s="0">
+        <v>10200.0</v>
+      </c>
+      <c r="BB11" t="n" s="0">
+        <v>12700.0</v>
+      </c>
+      <c r="BC11" t="n" s="0">
+        <v>15500.0</v>
+      </c>
+      <c r="BD11" t="n" s="0">
+        <v>24700.0</v>
+      </c>
+      <c r="BE11" t="n" s="0">
+        <v>9600.0</v>
+      </c>
+      <c r="BF11" t="n" s="0">
+        <v>14400.0</v>
+      </c>
+      <c r="BG11" t="n" s="0">
+        <v>9600.0</v>
+      </c>
+      <c r="BH11" t="n" s="0">
+        <v>9800.0</v>
+      </c>
+      <c r="BI11" t="n" s="0">
+        <v>11600.0</v>
+      </c>
+      <c r="BJ11" t="n" s="0">
+        <v>9500.0</v>
+      </c>
+      <c r="BK11" t="n" s="0">
+        <v>9600.0</v>
+      </c>
+      <c r="BL11" t="n" s="0">
+        <v>14700.0</v>
+      </c>
+      <c r="BM11" t="n" s="0">
+        <v>14000.0</v>
+      </c>
+      <c r="BN11" t="n" s="0">
         <v>16000.0</v>
       </c>
-      <c r="O11" t="n" s="0">
-        <v>16000.0</v>
-      </c>
-      <c r="P11" t="n" s="0">
-        <v>15200.0</v>
-      </c>
-      <c r="Q11" t="n" s="0">
+      <c r="BO11" t="n" s="0">
+        <v>13900.0</v>
+      </c>
+      <c r="BP11" t="n" s="0">
+        <v>20200.0</v>
+      </c>
+      <c r="BQ11" t="n" s="0">
+        <v>10900.0</v>
+      </c>
+      <c r="BR11" t="n" s="0">
+        <v>12200.0</v>
+      </c>
+      <c r="BS11" t="n" s="0">
+        <v>11200.0</v>
+      </c>
+      <c r="BT11" t="n" s="0">
+        <v>14300.0</v>
+      </c>
+      <c r="BU11" t="n" s="0">
+        <v>14600.0</v>
+      </c>
+      <c r="BV11" t="n" s="0">
+        <v>11500.0</v>
+      </c>
+      <c r="BW11" t="n" s="0">
+        <v>11200.0</v>
+      </c>
+      <c r="BX11" t="n" s="0">
+        <v>9700.0</v>
+      </c>
+      <c r="BY11" t="n" s="0">
         <v>10500.0</v>
       </c>
-      <c r="R11" t="n" s="0">
-        <v>18700.0</v>
-      </c>
-      <c r="S11" t="n" s="0">
-        <v>35500.0</v>
-      </c>
-      <c r="T11" t="n" s="0">
-        <v>19600.0</v>
-      </c>
-      <c r="U11" t="n" s="0">
-        <v>16700.0</v>
-      </c>
-      <c r="V11" t="n" s="0">
-        <v>17700.0</v>
-      </c>
-      <c r="W11" t="n" s="0">
-        <v>15200.0</v>
-      </c>
-      <c r="X11" t="n" s="0">
-        <v>16700.0</v>
-      </c>
-      <c r="Y11" t="n" s="0">
-        <v>15100.0</v>
-      </c>
-      <c r="Z11" t="n" s="0">
-        <v>26000.0</v>
-      </c>
-      <c r="AA11" t="n" s="0">
-        <v>17400.0</v>
-      </c>
-      <c r="AB11" t="n" s="0">
-        <v>25800.0</v>
-      </c>
-      <c r="AC11" t="n" s="0">
-        <v>23200.0</v>
-      </c>
-      <c r="AD11" t="n" s="0">
-        <v>15500.0</v>
-      </c>
-      <c r="AE11" t="n" s="0">
+      <c r="BZ11" t="n" s="0">
+        <v>15700.0</v>
+      </c>
+      <c r="CA11" t="n" s="0">
+        <v>11600.0</v>
+      </c>
+      <c r="CB11" t="n" s="0">
+        <v>11400.0</v>
+      </c>
+      <c r="CC11" t="n" s="0">
+        <v>9800.0</v>
+      </c>
+      <c r="CD11" t="n" s="0">
+        <v>12500.0</v>
+      </c>
+      <c r="CE11" t="n" s="0">
+        <v>13600.0</v>
+      </c>
+      <c r="CF11" t="n" s="0">
+        <v>14400.0</v>
+      </c>
+      <c r="CG11" t="n" s="0">
+        <v>14400.0</v>
+      </c>
+      <c r="CH11" t="n" s="0">
+        <v>12700.0</v>
+      </c>
+      <c r="CI11" t="n" s="0">
+        <v>10400.0</v>
+      </c>
+      <c r="CJ11" t="n" s="0">
+        <v>9200.0</v>
+      </c>
+      <c r="CK11" t="n" s="0">
+        <v>10600.0</v>
+      </c>
+      <c r="CL11" t="n" s="0">
         <v>13900.0</v>
       </c>
-      <c r="AF11" t="n" s="0">
-        <v>16400.0</v>
-      </c>
-      <c r="AG11" t="n" s="0">
-        <v>16700.0</v>
-      </c>
-      <c r="AH11" t="n" s="0">
-        <v>10600.0</v>
-      </c>
-      <c r="AI11" t="n" s="0">
-        <v>16000.0</v>
-      </c>
-      <c r="AJ11" t="n" s="0">
-        <v>17200.0</v>
-      </c>
-      <c r="AK11" t="n" s="0">
-        <v>31700.0</v>
-      </c>
-      <c r="AL11" t="n" s="0">
-        <v>16700.0</v>
-      </c>
-      <c r="AM11" t="n" s="0">
-        <v>19500.0</v>
-      </c>
-      <c r="AN11" t="n" s="0">
-        <v>182400.0</v>
-      </c>
-      <c r="AO11" t="n" s="0">
-        <v>15000.0</v>
-      </c>
-      <c r="AP11" t="n" s="0">
-        <v>13100.0</v>
-      </c>
-      <c r="AQ11" t="n" s="0">
-        <v>14900.0</v>
-      </c>
-      <c r="AR11" t="n" s="0">
-        <v>16300.0</v>
-      </c>
-      <c r="AS11" t="n" s="0">
-        <v>18100.0</v>
-      </c>
-      <c r="AT11" t="n" s="0">
-        <v>14800.0</v>
-      </c>
-      <c r="AU11" t="n" s="0">
-        <v>14700.0</v>
-      </c>
-      <c r="AV11" t="n" s="0">
-        <v>17000.0</v>
-      </c>
-      <c r="AW11" t="n" s="0">
-        <v>68000.0</v>
-      </c>
-      <c r="AX11" t="n" s="0">
-        <v>16000.0</v>
-      </c>
-      <c r="AY11" t="n" s="0">
-        <v>26000.0</v>
-      </c>
-      <c r="AZ11" t="n" s="0">
-        <v>14300.0</v>
+      <c r="CM11" t="n" s="0">
+        <v>13700.0</v>
+      </c>
+      <c r="CN11" t="n" s="0">
+        <v>11900.0</v>
+      </c>
+      <c r="CO11" t="n" s="0">
+        <v>9700.0</v>
+      </c>
+      <c r="CP11" t="n" s="0">
+        <v>11200.0</v>
+      </c>
+      <c r="CQ11" t="n" s="0">
+        <v>11100.0</v>
+      </c>
+      <c r="CR11" t="n" s="0">
+        <v>13500.0</v>
+      </c>
+      <c r="CS11" t="n" s="0">
+        <v>13500.0</v>
+      </c>
+      <c r="CT11" t="n" s="0">
+        <v>11200.0</v>
+      </c>
+      <c r="CU11" t="n" s="0">
+        <v>9100.0</v>
+      </c>
+      <c r="CV11" t="n" s="0">
+        <v>20800.0</v>
+      </c>
+      <c r="CW11" t="n" s="0">
+        <v>10900.0</v>
+      </c>
+      <c r="CX11" t="n" s="0">
+        <v>13400.0</v>
       </c>
     </row>
   </sheetData>
